--- a/Webprecios/files/LISTA DE PRECIOS WEB.xlsx
+++ b/Webprecios/files/LISTA DE PRECIOS WEB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastián\Desktop\SAMCOR\TodoEnUnoCompania\Webprecios\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E075774-C2F4-44E2-BA72-E2C72113E481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF43AC1E-3BF0-4922-8DB6-97A83517C8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86DE79B7-439B-BB49-B2A1-21F166C3998A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1393" uniqueCount="403">
   <si>
     <t>MEDIDA</t>
   </si>
@@ -50,63 +50,36 @@
     <t>PRECIO</t>
   </si>
   <si>
-    <t>500/R10</t>
-  </si>
-  <si>
     <t>CHINO</t>
   </si>
   <si>
-    <t>145/R12</t>
-  </si>
-  <si>
     <t>ROADMARCH</t>
   </si>
   <si>
     <t>PRIMEVAN 28</t>
   </si>
   <si>
-    <t>145/70/R12</t>
-  </si>
-  <si>
     <t>ECOPRO 99</t>
   </si>
   <si>
-    <t>155/70/R12</t>
-  </si>
-  <si>
-    <t>155/R12</t>
-  </si>
-  <si>
     <t>DUNLOP</t>
   </si>
   <si>
     <t>LT5</t>
   </si>
   <si>
-    <t>165/70/R12</t>
-  </si>
-  <si>
     <t>PRIMESTAR 66</t>
   </si>
   <si>
-    <t>500/R12</t>
-  </si>
-  <si>
     <t>GOODRIDE</t>
   </si>
   <si>
     <t>868 AT</t>
   </si>
   <si>
-    <t>550/R12</t>
-  </si>
-  <si>
     <t>SAILWIN</t>
   </si>
   <si>
-    <t>145/R13</t>
-  </si>
-  <si>
     <t>FROMWAY</t>
   </si>
   <si>
@@ -116,75 +89,21 @@
     <t>CP321</t>
   </si>
   <si>
-    <t>145/70/R13</t>
-  </si>
-  <si>
-    <t>155/R13</t>
-  </si>
-  <si>
-    <t>155/65/R13</t>
-  </si>
-  <si>
     <t>NPRIZ GX</t>
   </si>
   <si>
-    <t>155/70/R13</t>
-  </si>
-  <si>
-    <t>165/65/R13</t>
-  </si>
-  <si>
-    <t>165/70/R13</t>
-  </si>
-  <si>
-    <t>165/70/R13C</t>
-  </si>
-  <si>
-    <t>165/R13C</t>
-  </si>
-  <si>
     <t>HIFLY</t>
   </si>
   <si>
     <t>S2000</t>
   </si>
   <si>
-    <t>175/50/R13</t>
-  </si>
-  <si>
     <t>LM704</t>
   </si>
   <si>
-    <t>175/70/R13</t>
-  </si>
-  <si>
     <t>SPT1</t>
   </si>
   <si>
-    <t>175/R13</t>
-  </si>
-  <si>
-    <t>185/70/R13</t>
-  </si>
-  <si>
-    <t>550/R13C</t>
-  </si>
-  <si>
-    <t>600/R13C</t>
-  </si>
-  <si>
-    <t>155/60/R14</t>
-  </si>
-  <si>
-    <t>155/65/R14</t>
-  </si>
-  <si>
-    <t>165/55/R14</t>
-  </si>
-  <si>
-    <t>165/60/R14</t>
-  </si>
-  <si>
     <t>FALKEN</t>
   </si>
   <si>
@@ -194,63 +113,18 @@
     <t>SPR1</t>
   </si>
   <si>
-    <t>165/65/R14</t>
-  </si>
-  <si>
-    <t>165/70/R14</t>
-  </si>
-  <si>
-    <t>165/R14C</t>
-  </si>
-  <si>
     <t>LINGLONG</t>
   </si>
   <si>
-    <t>175/60/R14</t>
-  </si>
-  <si>
-    <t>175/65/R14</t>
-  </si>
-  <si>
-    <t>175/65/R14C</t>
-  </si>
-  <si>
     <t>PRIMEVAN 9</t>
   </si>
   <si>
-    <t>175/70/R14</t>
-  </si>
-  <si>
-    <t>175/70/R14C</t>
-  </si>
-  <si>
-    <t>175/R14</t>
-  </si>
-  <si>
     <t>PRIMEVAN 38</t>
   </si>
   <si>
-    <t>185/50/R14</t>
-  </si>
-  <si>
-    <t>185/55/R14</t>
-  </si>
-  <si>
-    <t>185/60/R14</t>
-  </si>
-  <si>
     <t>DZ102</t>
   </si>
   <si>
-    <t>185/65/R14</t>
-  </si>
-  <si>
-    <t>185/70/R14</t>
-  </si>
-  <si>
-    <t>185/R14</t>
-  </si>
-  <si>
     <t>PRIMEVAN 9 LET. BLANC.</t>
   </si>
   <si>
@@ -266,66 +140,21 @@
     <t>ROADIAN CT8</t>
   </si>
   <si>
-    <t>195/60/R14</t>
-  </si>
-  <si>
-    <t>195/70/R14</t>
-  </si>
-  <si>
-    <t>195/R14C</t>
-  </si>
-  <si>
-    <t>205/70/R14</t>
-  </si>
-  <si>
     <t>XBRI</t>
   </si>
   <si>
     <t>ECOLOGY</t>
   </si>
   <si>
-    <t>205/R14C</t>
-  </si>
-  <si>
-    <t>215/70/R14</t>
-  </si>
-  <si>
-    <t>215/75/R14</t>
-  </si>
-  <si>
-    <t>27/850/R14</t>
-  </si>
-  <si>
     <t>ALL TERRAIN</t>
   </si>
   <si>
-    <t>165/50/R15</t>
-  </si>
-  <si>
-    <t>175/55/R15</t>
-  </si>
-  <si>
-    <t>175/60/R15</t>
-  </si>
-  <si>
-    <t>175/65/R15</t>
-  </si>
-  <si>
     <t>RPIME AS</t>
   </si>
   <si>
-    <t>185/45/R15</t>
-  </si>
-  <si>
     <t>WINDFORCE</t>
   </si>
   <si>
-    <t>185/55/R15</t>
-  </si>
-  <si>
-    <t>185/60/R15</t>
-  </si>
-  <si>
     <t>PIRELLI</t>
   </si>
   <si>
@@ -338,24 +167,12 @@
     <t>CP672</t>
   </si>
   <si>
-    <t>185/65/R15</t>
-  </si>
-  <si>
-    <t>185/R15C</t>
-  </si>
-  <si>
-    <t>195/45/R15</t>
-  </si>
-  <si>
     <t>L-ZEAL56</t>
   </si>
   <si>
     <t>NFERA SU1</t>
   </si>
   <si>
-    <t>195/50/R15</t>
-  </si>
-  <si>
     <t>SUMITOMO</t>
   </si>
   <si>
@@ -368,18 +185,9 @@
     <t>MAXSPEED R1</t>
   </si>
   <si>
-    <t>195/55/R15</t>
-  </si>
-  <si>
     <t>MAXDRIFTING Z1</t>
   </si>
   <si>
-    <t>195/60/R15</t>
-  </si>
-  <si>
-    <t>195/65/R15</t>
-  </si>
-  <si>
     <t>PRIME AS</t>
   </si>
   <si>
@@ -389,54 +197,15 @@
     <t>PRIMESTAR 66 BLANCO</t>
   </si>
   <si>
-    <t>195/70/R15C</t>
-  </si>
-  <si>
-    <t>195/R15C</t>
-  </si>
-  <si>
-    <t>205/50/R15</t>
-  </si>
-  <si>
-    <t>205/55/R15</t>
-  </si>
-  <si>
-    <t>205/60/R15</t>
-  </si>
-  <si>
     <t>FORZA AT2</t>
   </si>
   <si>
-    <t>205/65/R15</t>
-  </si>
-  <si>
-    <t>205/70/R15C</t>
-  </si>
-  <si>
-    <t>205/70/R15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">205/70/R15 </t>
-  </si>
-  <si>
     <t>RADIAL 620</t>
   </si>
   <si>
     <t xml:space="preserve">MT </t>
   </si>
   <si>
-    <t>215/65/R15</t>
-  </si>
-  <si>
-    <t>215/70/R15</t>
-  </si>
-  <si>
-    <t>215/70/R15C</t>
-  </si>
-  <si>
-    <t>215/75/R15</t>
-  </si>
-  <si>
     <t>MIRAGE</t>
   </si>
   <si>
@@ -449,12 +218,6 @@
     <t>MT1</t>
   </si>
   <si>
-    <t>225/70/R15C</t>
-  </si>
-  <si>
-    <t>225/75/R15</t>
-  </si>
-  <si>
     <t>ZEXTOUR</t>
   </si>
   <si>
@@ -464,84 +227,30 @@
     <t>HT2</t>
   </si>
   <si>
-    <t>235/75/R15</t>
-  </si>
-  <si>
     <t>AT3</t>
   </si>
   <si>
     <t>PRIMEMASTER MT/2</t>
   </si>
   <si>
-    <t>255/60/R15</t>
-  </si>
-  <si>
     <t>HTR2000</t>
   </si>
   <si>
-    <t>265/70/R15</t>
-  </si>
-  <si>
-    <t>275/60/R15</t>
-  </si>
-  <si>
-    <t>295/50/R15</t>
-  </si>
-  <si>
-    <t>31/10.50/R15</t>
-  </si>
-  <si>
     <t>PRIMEMAX AT2</t>
   </si>
   <si>
-    <t>32/11.50/R15</t>
-  </si>
-  <si>
     <t>PRIMEMASTER MT/1</t>
   </si>
   <si>
-    <t>33/12.50/R15</t>
-  </si>
-  <si>
-    <t>35/12.50/R15</t>
-  </si>
-  <si>
-    <t>700/R15</t>
-  </si>
-  <si>
-    <t>175/50/R16</t>
-  </si>
-  <si>
-    <t>175/60/R16</t>
-  </si>
-  <si>
     <t>NBLUE HD</t>
   </si>
   <si>
-    <t>185/55/R16</t>
-  </si>
-  <si>
-    <t>185/60/R16</t>
-  </si>
-  <si>
-    <t>185/75/R16C</t>
-  </si>
-  <si>
     <t>LOADING PRO</t>
   </si>
   <si>
-    <t>195/45/R16</t>
-  </si>
-  <si>
     <t>PRIME UHP 08</t>
   </si>
   <si>
-    <t>195/50/R16</t>
-  </si>
-  <si>
-    <t>195/55/R16</t>
-  </si>
-  <si>
     <t>APTANY</t>
   </si>
   <si>
@@ -551,267 +260,78 @@
     <t>LM705</t>
   </si>
   <si>
-    <t>195/60/R16C</t>
-  </si>
-  <si>
-    <t>195/60/R16</t>
-  </si>
-  <si>
     <t>NBLUE ECO</t>
   </si>
   <si>
-    <t>195/65/R16C</t>
-  </si>
-  <si>
-    <t>195/75/R16C</t>
-  </si>
-  <si>
-    <t>205/45/R16</t>
-  </si>
-  <si>
-    <t>205/50/R16</t>
-  </si>
-  <si>
-    <t>205/55/R16</t>
-  </si>
-  <si>
-    <t>205/60/R16</t>
-  </si>
-  <si>
-    <t>205/65/R16</t>
-  </si>
-  <si>
-    <t>205/65/R16C</t>
-  </si>
-  <si>
-    <t>205/70/R16</t>
-  </si>
-  <si>
     <t>NPRIZ AH8</t>
   </si>
   <si>
-    <t>205/75/R16C</t>
-  </si>
-  <si>
-    <t>215/40/R16</t>
-  </si>
-  <si>
-    <t>215/45/R16</t>
-  </si>
-  <si>
-    <t>215/55/R16</t>
-  </si>
-  <si>
     <t>NFERA SU4</t>
   </si>
   <si>
-    <t>215/60/R16</t>
-  </si>
-  <si>
-    <t>215/60/R16C</t>
-  </si>
-  <si>
-    <t>215/65/R16</t>
-  </si>
-  <si>
-    <t>215/65/R16C</t>
-  </si>
-  <si>
-    <t>215/70/R16C</t>
-  </si>
-  <si>
-    <t>215/70/R16</t>
-  </si>
-  <si>
     <t>PRIMEMARCH HT79</t>
   </si>
   <si>
     <t>NB 4 SEASON</t>
   </si>
   <si>
-    <t>215/85/R16</t>
-  </si>
-  <si>
-    <t>225/50/R16</t>
-  </si>
-  <si>
-    <t>225/55/R16</t>
-  </si>
-  <si>
-    <t>225/65/R16C</t>
-  </si>
-  <si>
-    <t>225/65/R16</t>
-  </si>
-  <si>
-    <t>225/70/R16</t>
-  </si>
-  <si>
-    <t>225/75/R16C</t>
-  </si>
-  <si>
     <t>DOUEBLE KING</t>
   </si>
   <si>
     <t>AT CARGA</t>
   </si>
   <si>
-    <t>235/60/R16</t>
-  </si>
-  <si>
-    <t>235/65/R16</t>
-  </si>
-  <si>
-    <t>235/65/R16C</t>
-  </si>
-  <si>
     <t>PRIMEVAN</t>
   </si>
   <si>
-    <t>235/70/R16</t>
-  </si>
-  <si>
     <t>PRIMEMARCH HT77</t>
   </si>
   <si>
-    <t>235/85/R16</t>
-  </si>
-  <si>
-    <t>245/70/R16</t>
-  </si>
-  <si>
-    <t>245/75/R16</t>
-  </si>
-  <si>
-    <t>255/70/R16</t>
-  </si>
-  <si>
     <t>AT PRO RA8</t>
   </si>
   <si>
-    <t>265/70/R16</t>
-  </si>
-  <si>
-    <t>265/75/R16</t>
-  </si>
-  <si>
-    <t>285/75/R16</t>
-  </si>
-  <si>
-    <t>305/70/R16</t>
-  </si>
-  <si>
-    <t>315/75/R16</t>
-  </si>
-  <si>
-    <t>650/R16</t>
-  </si>
-  <si>
-    <t>700/R16</t>
-  </si>
-  <si>
     <t>GLORY TOUR 52</t>
   </si>
   <si>
-    <t>750/R16</t>
-  </si>
-  <si>
-    <t>195/40/R17</t>
-  </si>
-  <si>
     <t>LING LONG</t>
   </si>
   <si>
     <t>GREEN MAX UHP</t>
   </si>
   <si>
-    <t>195/45/R17</t>
-  </si>
-  <si>
-    <t>205/40/R17</t>
-  </si>
-  <si>
     <t>DZ101</t>
   </si>
   <si>
-    <t>205/45/R17</t>
-  </si>
-  <si>
     <t>RUNFLAT</t>
   </si>
   <si>
-    <t>205/50/R17</t>
-  </si>
-  <si>
-    <t>205/55/R17</t>
-  </si>
-  <si>
-    <t>215/40/R17</t>
-  </si>
-  <si>
     <t>SPORT 2</t>
   </si>
   <si>
-    <t>215/45/R17</t>
-  </si>
-  <si>
-    <t>215/50/R17</t>
-  </si>
-  <si>
-    <t>215/55/R17</t>
-  </si>
-  <si>
     <t>CP671</t>
   </si>
   <si>
-    <t>215/60/R17</t>
-  </si>
-  <si>
-    <t>215/60/R17C</t>
-  </si>
-  <si>
-    <t>215/65/R17</t>
-  </si>
-  <si>
     <t>ZE914</t>
   </si>
   <si>
-    <t>215/75/R17.5</t>
-  </si>
-  <si>
     <t>ECOPLUS A2V (DIRECC)</t>
   </si>
   <si>
     <t>ROBUSTO A2 (TRACC)</t>
   </si>
   <si>
-    <t>225/45/R17</t>
-  </si>
-  <si>
-    <t>225/50/R17</t>
-  </si>
-  <si>
     <t>SPFM800</t>
   </si>
   <si>
-    <t>225/55/R17</t>
-  </si>
-  <si>
     <t>MAXX TT</t>
   </si>
   <si>
     <t>CP643A</t>
   </si>
   <si>
-    <t>225/60/R17</t>
-  </si>
-  <si>
     <t>PT3</t>
   </si>
   <si>
-    <t>225/65/R17</t>
-  </si>
-  <si>
     <t>WANLI</t>
   </si>
   <si>
@@ -821,24 +341,12 @@
     <t>AT5</t>
   </si>
   <si>
-    <t>235/45/R17</t>
-  </si>
-  <si>
-    <t>235/55/R17</t>
-  </si>
-  <si>
     <t>DURABLE</t>
   </si>
   <si>
     <t>SPORT D</t>
   </si>
   <si>
-    <t>235/60/R17</t>
-  </si>
-  <si>
-    <t>235/65/R17</t>
-  </si>
-  <si>
     <t>PRIMEMAX AT1</t>
   </si>
   <si>
@@ -854,84 +362,21 @@
     <t>KRUGEN KL33</t>
   </si>
   <si>
-    <t>245/65/R17</t>
-  </si>
-  <si>
-    <t>245/70/R17</t>
-  </si>
-  <si>
     <t>CHAOYANG</t>
   </si>
   <si>
-    <t>245/75/R17</t>
-  </si>
-  <si>
-    <t>265/65/R17</t>
-  </si>
-  <si>
-    <t>265/70/R17</t>
-  </si>
-  <si>
-    <t>275/60/R17</t>
-  </si>
-  <si>
     <t>ROADIAN HP</t>
   </si>
   <si>
-    <t>275/65/R17</t>
-  </si>
-  <si>
-    <t>275/70/R17</t>
-  </si>
-  <si>
     <t xml:space="preserve">ALL TERRAIN  </t>
   </si>
   <si>
-    <t>285/65/R17</t>
-  </si>
-  <si>
-    <t>285/70/R17</t>
-  </si>
-  <si>
-    <t>315/70/R17</t>
-  </si>
-  <si>
-    <t>33/12.50/R17</t>
-  </si>
-  <si>
-    <t>35/12.50/R17</t>
-  </si>
-  <si>
-    <t>215/35/R18</t>
-  </si>
-  <si>
-    <t>215/40/R18</t>
-  </si>
-  <si>
-    <t>215/45/R18</t>
-  </si>
-  <si>
     <t>FK453</t>
   </si>
   <si>
     <t>SPORT MAXX TT</t>
   </si>
   <si>
-    <t>215/50/R18</t>
-  </si>
-  <si>
-    <t>215/55/R18</t>
-  </si>
-  <si>
-    <t>225/40/R18</t>
-  </si>
-  <si>
-    <t>225/45/R18</t>
-  </si>
-  <si>
-    <t>225/50/R18</t>
-  </si>
-  <si>
     <t>SPORT MAXX 050</t>
   </si>
   <si>
@@ -941,9 +386,6 @@
     <t>ALENZA</t>
   </si>
   <si>
-    <t>225/55/R18</t>
-  </si>
-  <si>
     <t>NPRIZ RH7</t>
   </si>
   <si>
@@ -956,298 +398,853 @@
     <t>PRIMACY 4</t>
   </si>
   <si>
-    <t>225/60/R18</t>
-  </si>
-  <si>
-    <t>235/40/R18</t>
-  </si>
-  <si>
-    <t>235/45/R18</t>
-  </si>
-  <si>
-    <t>235/50/R18</t>
-  </si>
-  <si>
-    <t>235/55/R18</t>
-  </si>
-  <si>
-    <t>235/60/R18</t>
-  </si>
-  <si>
-    <t>235/65/R18</t>
-  </si>
-  <si>
-    <t>245/35/R18</t>
-  </si>
-  <si>
     <t>ROADX</t>
   </si>
   <si>
     <t>U11</t>
   </si>
   <si>
-    <t>245/40/R18</t>
-  </si>
-  <si>
-    <t>245/45/R18</t>
-  </si>
-  <si>
     <t>EURUS 08</t>
   </si>
   <si>
-    <t>245/50/R18</t>
-  </si>
-  <si>
-    <t>245/60/R18</t>
-  </si>
-  <si>
-    <t>255/35/R18</t>
-  </si>
-  <si>
-    <t>255/40/R18</t>
-  </si>
-  <si>
-    <t>255/55/R18</t>
-  </si>
-  <si>
-    <t>255/60/R18</t>
-  </si>
-  <si>
-    <t>265/35/R18</t>
-  </si>
-  <si>
-    <t>265/60/R18</t>
-  </si>
-  <si>
     <t>SU318</t>
   </si>
   <si>
     <t>AT20</t>
   </si>
   <si>
-    <t>265/65/R18</t>
-  </si>
-  <si>
-    <t>275/35/R18</t>
-  </si>
-  <si>
-    <t>275/40/R18</t>
-  </si>
-  <si>
-    <t>275/65/R18</t>
-  </si>
-  <si>
-    <t>275/70/R18</t>
-  </si>
-  <si>
     <t>CATCHFORS AT2</t>
   </si>
   <si>
-    <t>285/60/R18</t>
-  </si>
-  <si>
-    <t>285/65/R18</t>
-  </si>
-  <si>
     <t>AT3W</t>
   </si>
   <si>
-    <t>305/60/R18</t>
-  </si>
-  <si>
-    <t>33/12.50/R18</t>
-  </si>
-  <si>
-    <t>225/35/R19</t>
-  </si>
-  <si>
-    <t>225/40/R19</t>
-  </si>
-  <si>
-    <t>225/45/R19</t>
-  </si>
-  <si>
     <t>AUTOGREEN</t>
   </si>
   <si>
     <t>FK510</t>
   </si>
   <si>
-    <t>225/55/R19</t>
-  </si>
-  <si>
-    <t>235/35/R19</t>
-  </si>
-  <si>
-    <t>235/40/R19</t>
-  </si>
-  <si>
-    <t>235/45/R19</t>
-  </si>
-  <si>
-    <t>235/50/R19</t>
-  </si>
-  <si>
-    <t>235/55/R19</t>
-  </si>
-  <si>
-    <t>245/35/R19</t>
-  </si>
-  <si>
-    <t>245/40/R19</t>
-  </si>
-  <si>
     <t>SPORT MAXX</t>
   </si>
   <si>
-    <t>245/45/R19</t>
-  </si>
-  <si>
-    <t>255/35/R19</t>
-  </si>
-  <si>
-    <t>255/40/R19</t>
-  </si>
-  <si>
-    <t>255/45/R19</t>
-  </si>
-  <si>
-    <t>255/50/R19</t>
-  </si>
-  <si>
-    <t>255/55/R19</t>
-  </si>
-  <si>
-    <t>275/35/R19</t>
-  </si>
-  <si>
-    <t>275/40/R19</t>
-  </si>
-  <si>
-    <t>235/35/R20</t>
-  </si>
-  <si>
-    <t>235/55/R20</t>
-  </si>
-  <si>
     <t>NFERA RU5</t>
   </si>
   <si>
-    <t>245/35/R20</t>
-  </si>
-  <si>
-    <t>245/40/R20</t>
-  </si>
-  <si>
-    <t>245/45/R20</t>
-  </si>
-  <si>
     <t>RYDANZ</t>
   </si>
   <si>
-    <t>255/35/R20</t>
-  </si>
-  <si>
-    <t>255/45/R20</t>
-  </si>
-  <si>
-    <t>255/50/R20</t>
-  </si>
-  <si>
     <t>PRIME UHP 07</t>
   </si>
   <si>
-    <t>255/55/R20</t>
-  </si>
-  <si>
-    <t>265/45/R20</t>
-  </si>
-  <si>
-    <t>265/50/R20</t>
-  </si>
-  <si>
-    <t>265/55/R20</t>
-  </si>
-  <si>
-    <t>265/60/R20</t>
-  </si>
-  <si>
     <t>BRUTUS TA</t>
   </si>
   <si>
-    <t>275/35/R20</t>
-  </si>
-  <si>
-    <t>275/40/R20</t>
-  </si>
-  <si>
-    <t>275/45/R20</t>
-  </si>
-  <si>
     <t>LS669</t>
   </si>
   <si>
-    <t>275/50/R20</t>
-  </si>
-  <si>
-    <t>275/55/R20</t>
-  </si>
-  <si>
-    <t>275/60/R20</t>
-  </si>
-  <si>
     <t>ROADCRUZA</t>
   </si>
   <si>
-    <t>285/30/R20</t>
-  </si>
-  <si>
-    <t>285/50/R20</t>
-  </si>
-  <si>
     <t>SPORTLINE</t>
   </si>
   <si>
-    <t>285/55/R20</t>
-  </si>
-  <si>
-    <t>305/50/R20</t>
-  </si>
-  <si>
-    <t>315/35/R20</t>
-  </si>
-  <si>
-    <t>33/12.50/R20</t>
-  </si>
-  <si>
-    <t>35/12.50/R20</t>
-  </si>
-  <si>
-    <t>265/45/R21</t>
-  </si>
-  <si>
-    <t>275/45/R21</t>
-  </si>
-  <si>
-    <t>275/50/R21</t>
-  </si>
-  <si>
-    <t>295/35/R21</t>
-  </si>
-  <si>
-    <t>295/40/R21</t>
-  </si>
-  <si>
-    <t>265/35/R22</t>
-  </si>
-  <si>
-    <t>265/40/R22</t>
-  </si>
-  <si>
-    <t>285/50/R22</t>
-  </si>
-  <si>
-    <t>33/12.50/R22</t>
+    <t xml:space="preserve">500R10  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">145R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">145/70R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155/70R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/70R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">500R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">550R12  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">145R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">145/70R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155/65R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155/70R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/65R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/70R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/70R13C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165R13C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/50R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/70R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/70R13  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">550R13C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">600R13C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155/60R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">155/65R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/55R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/60R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/65R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165R14C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/60R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/65R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/65R14C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/70R14C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/50R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/55R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/60R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/65R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/60R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195R14C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205R14C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/70R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/75R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/850R14  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">165/50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/55R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/65R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/45R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/55R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/65R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/45R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/55R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/65R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/70R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/55R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/65R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/70R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/70R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/65R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/70R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/70R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/75R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/70R15C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/75R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/75R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/70R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/60R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">295/50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/10.50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">32/11.50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33/12.50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35/12.50R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">700R15  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/50R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">175/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/55R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">185/75R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/45R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/50R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/55R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/60R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/65R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/75R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/45R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/50R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/55R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/65R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/65R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/75R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/40R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/45R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/55R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/60R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/65R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/65R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/70R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/85R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/50R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/55R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/65R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/65R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/75R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/60R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/65R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/65R16C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/85R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/75R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/75R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/75R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">305/70R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">315/75R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">650R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">700R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">750R16  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/40R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">195/45R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/40R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/45R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/50R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">205/55R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/40R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/45R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/50R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/55R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/60R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/60R17C  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/75R17.5  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/45R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/50R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/55R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/60R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/45R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/55R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/60R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/70R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/75R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/70R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/60R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/70R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/65R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/70R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">315/70R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33/12.50R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35/12.50R17  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/35R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/45R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/50R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">215/55R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/45R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/50R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/55R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/45R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/50R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/55R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/65R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/35R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/45R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/50R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/35R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/55R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/35R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/65R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/35R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/40R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/65R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/70R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/65R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">305/60R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33/12.50R18  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/35R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/40R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/45R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">225/55R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/35R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/40R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/45R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/50R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/55R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/35R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/40R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/45R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/35R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/40R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/45R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/50R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/55R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/35R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/40R19  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/35R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">235/55R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/35R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/40R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">245/45R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/35R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/45R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">255/55R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/45R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/55R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/60R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/35R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/40R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/45R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/55R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/60R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/30R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/55R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">305/50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">315/35R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33/12.50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35/12.50R20  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/45R21  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/45R21  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">275/50R21  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">295/35R21  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">295/40R21  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/35R22  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">265/40R22  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">285/50R22  </t>
+  </si>
+  <si>
+    <t>33/12.50R22</t>
   </si>
 </sst>
 </file>
@@ -1443,18 +1440,6 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1532,13 +1517,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -1551,6 +1529,25 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -1567,13 +1564,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6F68FCBE-A31E-41DE-9D94-B0DA28C9FC73}" name="Tabla1" displayName="Tabla1" ref="A1:D467" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6F68FCBE-A31E-41DE-9D94-B0DA28C9FC73}" name="Tabla1" displayName="Tabla1" ref="A1:D467" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:D467" xr:uid="{6F68FCBE-A31E-41DE-9D94-B0DA28C9FC73}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{02E9608F-421E-44C5-9404-C679BF44AEB1}" name="MEDIDA" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{B1F8A53A-B13B-4A51-9F79-8D8EF4956E9C}" name="MARCA" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{55DFEDBF-D19F-48E9-9EF1-52AC0DF1A0E7}" name="MODELO" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{DB7A0A06-AF64-47E9-9A7F-045CA06D591C}" name="PRECIO" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{02E9608F-421E-44C5-9404-C679BF44AEB1}" name="MEDIDA" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{B1F8A53A-B13B-4A51-9F79-8D8EF4956E9C}" name="MARCA" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{55DFEDBF-D19F-48E9-9EF1-52AC0DF1A0E7}" name="MODELO" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{DB7A0A06-AF64-47E9-9A7F-045CA06D591C}" name="PRECIO" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1919,10 +1916,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="6">
@@ -1931,13 +1928,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="6">
         <v>45000</v>
@@ -1945,13 +1942,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>139</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="6">
         <v>35000</v>
@@ -1959,13 +1956,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>140</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D5" s="6">
         <v>35000</v>
@@ -1973,13 +1970,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6">
         <v>50000</v>
@@ -1987,13 +1984,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>141</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6">
         <v>40000</v>
@@ -2001,13 +1998,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D8" s="6">
         <v>40000</v>
@@ -2015,13 +2012,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D9" s="6">
         <v>50000</v>
@@ -2029,13 +2026,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D10" s="6">
         <v>50000</v>
@@ -2043,13 +2040,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="6">
         <v>55000</v>
@@ -2057,13 +2054,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D12" s="6">
         <v>50000</v>
@@ -2071,13 +2068,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>145</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D13" s="6">
         <v>60000</v>
@@ -2085,13 +2082,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D14" s="6">
         <v>40000</v>
@@ -2099,13 +2096,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>147</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6">
         <v>50000</v>
@@ -2113,13 +2110,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D16" s="6">
         <v>35000</v>
@@ -2127,13 +2124,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D17" s="6">
         <v>55000</v>
@@ -2141,13 +2138,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>30</v>
+        <v>149</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D18" s="6">
         <v>40000</v>
@@ -2155,13 +2152,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D19" s="6">
         <v>40000</v>
@@ -2169,13 +2166,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>151</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D20" s="6">
         <v>40000</v>
@@ -2183,13 +2180,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>33</v>
+        <v>152</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D21" s="6">
         <v>45000</v>
@@ -2197,13 +2194,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>153</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6">
         <v>50000</v>
@@ -2211,13 +2208,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D23" s="6">
         <v>70000</v>
@@ -2225,13 +2222,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D24" s="6">
         <v>55000</v>
@@ -2239,13 +2236,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D25" s="6">
         <v>40000</v>
@@ -2253,13 +2250,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>39</v>
+        <v>155</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D26" s="6">
         <v>60000</v>
@@ -2267,13 +2264,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>41</v>
+        <v>156</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D27" s="6">
         <v>65000</v>
@@ -2281,13 +2278,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>42</v>
+        <v>157</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D28" s="6">
         <v>45000</v>
@@ -2295,13 +2292,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>43</v>
+        <v>158</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D29" s="6">
         <v>55000</v>
@@ -2309,10 +2306,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>44</v>
+        <v>159</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="6">
@@ -2321,13 +2318,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D31" s="6">
         <v>45000</v>
@@ -2335,13 +2332,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D32" s="6">
         <v>40000</v>
@@ -2349,13 +2346,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="4" t="s">
-        <v>47</v>
+        <v>162</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D33" s="6">
         <v>45000</v>
@@ -2363,13 +2360,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D34" s="6">
         <v>40000</v>
@@ -2377,13 +2374,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D35" s="6">
         <v>55000</v>
@@ -2391,13 +2388,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D36" s="6">
         <v>60000</v>
@@ -2405,13 +2402,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
-        <v>48</v>
+        <v>163</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D37" s="6">
         <v>70000</v>
@@ -2419,13 +2416,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="4" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D38" s="6">
         <v>45000</v>
@@ -2433,13 +2430,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D39" s="6">
         <v>75000</v>
@@ -2447,13 +2444,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D40" s="6">
         <v>60000</v>
@@ -2461,13 +2458,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D41" s="6">
         <v>45000</v>
@@ -2475,13 +2472,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="4" t="s">
-        <v>53</v>
+        <v>165</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D42" s="6">
         <v>60000</v>
@@ -2489,13 +2486,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="4" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D43" s="6">
         <v>55000</v>
@@ -2503,10 +2500,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="6">
@@ -2515,13 +2512,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="4" t="s">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="B45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D45" s="6">
         <v>45000</v>
@@ -2529,13 +2526,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="4" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D46" s="6">
         <v>55000</v>
@@ -2543,13 +2540,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D47" s="6">
         <v>45000</v>
@@ -2557,13 +2554,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="4" t="s">
-        <v>57</v>
+        <v>168</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D48" s="6">
         <v>70000</v>
@@ -2571,13 +2568,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="4" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D49" s="6">
         <v>55000</v>
@@ -2585,13 +2582,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="4" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="B50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D50" s="6">
         <v>45000</v>
@@ -2599,13 +2596,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="4" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D51" s="6">
         <v>60000</v>
@@ -2613,13 +2610,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="4" t="s">
-        <v>61</v>
+        <v>171</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D52" s="6">
         <v>55000</v>
@@ -2627,13 +2624,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D53" s="6">
         <v>77000</v>
@@ -2641,13 +2638,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="4" t="s">
-        <v>62</v>
+        <v>172</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="D54" s="6">
         <v>65000</v>
@@ -2655,13 +2652,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="4" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D55" s="6">
         <v>50000</v>
@@ -2669,13 +2666,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="4" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D56" s="6">
         <v>50000</v>
@@ -2683,13 +2680,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="4" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D57" s="6">
         <v>80000</v>
@@ -2697,13 +2694,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="4" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D58" s="6">
         <v>55000</v>
@@ -2711,13 +2708,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D59" s="6">
         <v>45000</v>
@@ -2725,13 +2722,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D60" s="6">
         <v>75000</v>
@@ -2739,13 +2736,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D61" s="6">
         <v>60000</v>
@@ -2753,13 +2750,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D62" s="6">
         <v>45000</v>
@@ -2767,13 +2764,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>177</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D63" s="6">
         <v>50000</v>
@@ -2781,13 +2778,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D64" s="6">
         <v>70000</v>
@@ -2795,13 +2792,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D65" s="6">
         <v>65000</v>
@@ -2809,13 +2806,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="4" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D66" s="6">
         <v>75000</v>
@@ -2823,13 +2820,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="4" t="s">
-        <v>70</v>
+        <v>178</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="D67" s="6">
         <v>80000</v>
@@ -2837,13 +2834,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="4" t="s">
-        <v>76</v>
+        <v>179</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D68" s="6">
         <v>50000</v>
@@ -2851,13 +2848,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="4" t="s">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D69" s="6">
         <v>50000</v>
@@ -2865,13 +2862,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="4" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D70" s="6">
         <v>63000</v>
@@ -2879,13 +2876,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D71" s="6">
         <v>75000</v>
@@ -2893,13 +2890,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D72" s="6">
         <v>80000</v>
@@ -2907,13 +2904,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>182</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="D73" s="6">
         <v>60000</v>
@@ -2921,13 +2918,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="4" t="s">
-        <v>82</v>
+        <v>183</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D74" s="6">
         <v>75000</v>
@@ -2935,13 +2932,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="4" t="s">
-        <v>83</v>
+        <v>184</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D75" s="6">
         <v>65000</v>
@@ -2949,13 +2946,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="4" t="s">
-        <v>84</v>
+        <v>185</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D76" s="6">
         <v>75000</v>
@@ -2963,13 +2960,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="4" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D77" s="6">
         <v>80000</v>
@@ -2977,13 +2974,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="4" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D78" s="6">
         <v>90000</v>
@@ -2991,13 +2988,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="4" t="s">
-        <v>87</v>
+        <v>187</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D79" s="6">
         <v>50000</v>
@@ -3005,13 +3002,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="4" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="B80" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D80" s="6">
         <v>55000</v>
@@ -3019,13 +3016,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="4" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="B81" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D81" s="6">
         <v>50000</v>
@@ -3033,13 +3030,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="4" t="s">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="D82" s="6">
         <v>50000</v>
@@ -3047,10 +3044,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="4" t="s">
-        <v>92</v>
+        <v>191</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="6">
@@ -3059,13 +3056,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="4" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D84" s="6">
         <v>75000</v>
@@ -3073,13 +3070,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="4" t="s">
-        <v>94</v>
+        <v>192</v>
       </c>
       <c r="B85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D85" s="6">
         <v>50000</v>
@@ -3087,13 +3084,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="4" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D86" s="6">
         <v>85000</v>
@@ -3101,13 +3098,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="4" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="D87" s="6">
         <v>85000</v>
@@ -3115,13 +3112,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="4" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="D88" s="6">
         <v>70000</v>
@@ -3129,13 +3126,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="4" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D89" s="6">
         <v>75000</v>
@@ -3143,13 +3140,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="4" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="B90" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D90" s="6">
         <v>50000</v>
@@ -3157,13 +3154,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="4" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="B91" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D91" s="6">
         <v>50000</v>
@@ -3171,13 +3168,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="4" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D92" s="6">
         <v>85000</v>
@@ -3185,13 +3182,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="4" t="s">
-        <v>100</v>
+        <v>194</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D93" s="6">
         <v>80000</v>
@@ -3199,13 +3196,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="4" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D94" s="6">
         <v>70000</v>
@@ -3213,13 +3210,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="5" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D95" s="7">
         <v>50000</v>
@@ -3227,13 +3224,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="5" t="s">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D96" s="7">
         <v>80000</v>
@@ -3241,13 +3238,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D97" s="7">
         <v>50000</v>
@@ -3255,13 +3252,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D98" s="6">
         <v>95000</v>
@@ -3269,13 +3266,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="D99" s="6">
         <v>70000</v>
@@ -3283,13 +3280,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D100" s="6">
         <v>75000</v>
@@ -3297,13 +3294,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="4" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="D101" s="6">
         <v>55000</v>
@@ -3311,13 +3308,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B102" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D102" s="6">
         <v>50000</v>
@@ -3325,13 +3322,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D103" s="6">
         <v>100000</v>
@@ -3339,13 +3336,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D104" s="6">
         <v>75000</v>
@@ -3353,13 +3350,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="D105" s="6">
         <v>53000</v>
@@ -3367,13 +3364,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="4" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="D106" s="6">
         <v>53000</v>
@@ -3381,13 +3378,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="4" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D107" s="6">
         <v>75000</v>
@@ -3395,13 +3392,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="4" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D108" s="6">
         <v>70000</v>
@@ -3409,13 +3406,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="4" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B109" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D109" s="6">
         <v>50000</v>
@@ -3423,13 +3420,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="4" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D110" s="6">
         <v>50000</v>
@@ -3437,13 +3434,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="4" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="D111" s="6">
         <v>75000</v>
@@ -3451,13 +3448,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="4" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D112" s="6">
         <v>85000</v>
@@ -3465,13 +3462,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="4" t="s">
-        <v>113</v>
+        <v>200</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
       <c r="D113" s="6">
         <v>55000</v>
@@ -3479,13 +3476,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="4" t="s">
-        <v>117</v>
+        <v>201</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D114" s="6">
         <v>75000</v>
@@ -3493,13 +3490,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D115" s="6">
         <v>75000</v>
@@ -3507,13 +3504,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="D116" s="6">
         <v>85000</v>
@@ -3521,13 +3518,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="4" t="s">
-        <v>118</v>
+        <v>202</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="D117" s="6">
         <v>90000</v>
@@ -3535,13 +3532,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="4" t="s">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D118" s="6">
         <v>55000</v>
@@ -3549,13 +3546,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="4" t="s">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D119" s="6">
         <v>105000</v>
@@ -3563,13 +3560,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="4" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D120" s="6">
         <v>55000</v>
@@ -3577,13 +3574,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="4" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D121" s="6">
         <v>75000</v>
@@ -3591,13 +3588,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="4" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="D122" s="6">
         <v>65000</v>
@@ -3605,13 +3602,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="4" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="B123" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D123" s="6">
         <v>55000</v>
@@ -3619,13 +3616,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="4" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>122</v>
+        <v>53</v>
       </c>
       <c r="D124" s="6">
         <v>70000</v>
@@ -3633,13 +3630,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="B125" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D125" s="6">
         <v>55000</v>
@@ -3647,13 +3644,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="4" t="s">
-        <v>123</v>
+        <v>206</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D126" s="6">
         <v>90000</v>
@@ -3661,13 +3658,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="4" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D127" s="6">
         <v>75000</v>
@@ -3675,13 +3672,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="4" t="s">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D128" s="6">
         <v>65000</v>
@@ -3689,13 +3686,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="4" t="s">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D129" s="6">
         <v>75000</v>
@@ -3703,13 +3700,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="4" t="s">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="D130" s="6">
         <v>85000</v>
@@ -3717,13 +3714,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="4" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D131" s="6">
         <v>65000</v>
@@ -3731,13 +3728,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="4" t="s">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D132" s="6">
         <v>65000</v>
@@ -3745,13 +3742,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="4" t="s">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D133" s="6">
         <v>75000</v>
@@ -3759,13 +3756,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="4" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D134" s="6">
         <v>80000</v>
@@ -3773,13 +3770,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="4" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="D135" s="6">
         <v>70000</v>
@@ -3787,13 +3784,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="4" t="s">
-        <v>132</v>
+        <v>212</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="D136" s="6">
         <v>100000</v>
@@ -3801,13 +3798,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="4" t="s">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D137" s="6">
         <v>85000</v>
@@ -3815,13 +3812,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="4" t="s">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D138" s="6">
         <v>90000</v>
@@ -3829,13 +3826,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="4" t="s">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="D139" s="6">
         <v>70000</v>
@@ -3843,13 +3840,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="4" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D140" s="6">
         <v>95000</v>
@@ -3857,13 +3854,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="4" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D141" s="6">
         <v>110000</v>
@@ -3871,13 +3868,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="4" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="D142" s="6">
         <v>80000</v>
@@ -3885,13 +3882,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="4" t="s">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D143" s="6">
         <v>110000</v>
@@ -3899,13 +3896,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="4" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="D144" s="6">
         <v>160000</v>
@@ -3913,13 +3910,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="4" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>143</v>
+        <v>63</v>
       </c>
       <c r="D145" s="6">
         <v>110000</v>
@@ -3927,13 +3924,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="4" t="s">
-        <v>147</v>
+        <v>217</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D146" s="6">
         <v>95000</v>
@@ -3941,13 +3938,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="4" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="D147" s="6">
         <v>170000</v>
@@ -3955,13 +3952,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="4" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="D148" s="6">
         <v>190000</v>
@@ -3969,13 +3966,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="4" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D149" s="6">
         <v>120000</v>
@@ -3983,13 +3980,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="4" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D150" s="6">
         <v>120000</v>
@@ -3997,13 +3994,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="4" t="s">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D151" s="6">
         <v>110000</v>
@@ -4011,13 +4008,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="4" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D152" s="6">
         <v>150000</v>
@@ -4025,13 +4022,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="4" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D153" s="6">
         <v>165000</v>
@@ -4039,13 +4036,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="4" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D154" s="6">
         <v>175000</v>
@@ -4053,10 +4050,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="4" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="6">
@@ -4065,13 +4062,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="4" t="s">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D156" s="6">
         <v>60000</v>
@@ -4079,13 +4076,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="4" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>159</v>
+        <v>68</v>
       </c>
       <c r="D157" s="6">
         <v>90000</v>
@@ -4093,13 +4090,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="4" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D158" s="6">
         <v>60000</v>
@@ -4107,13 +4104,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="4" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D159" s="6">
         <v>95000</v>
@@ -4121,13 +4118,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="4" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D160" s="6">
         <v>95000</v>
@@ -4135,13 +4132,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="4" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D161" s="6">
         <v>60000</v>
@@ -4149,13 +4146,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="4" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>163</v>
+        <v>69</v>
       </c>
       <c r="D162" s="6">
         <v>80000</v>
@@ -4163,13 +4160,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="4" t="s">
-        <v>164</v>
+        <v>230</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D163" s="6">
         <v>60000</v>
@@ -4177,13 +4174,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="4" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="B164" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D164" s="6">
         <v>60000</v>
@@ -4191,13 +4188,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="4" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D165" s="6">
         <v>100000</v>
@@ -4205,13 +4202,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="4" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D166" s="6">
         <v>85000</v>
@@ -4219,13 +4216,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="4" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D167" s="6">
         <v>60000</v>
@@ -4233,13 +4230,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="4" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="D168" s="6">
         <v>100000</v>
@@ -4247,13 +4244,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="4" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D169" s="6">
         <v>90000</v>
@@ -4261,13 +4258,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="4" t="s">
-        <v>167</v>
+        <v>232</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="D170" s="6">
         <v>110000</v>
@@ -4275,13 +4272,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="4" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D171" s="6">
         <v>75000</v>
@@ -4289,13 +4286,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="4" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>173</v>
+        <v>74</v>
       </c>
       <c r="D172" s="6">
         <v>75000</v>
@@ -4303,13 +4300,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="4" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D173" s="6">
         <v>60000</v>
@@ -4317,13 +4314,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="4" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D174" s="6">
         <v>75000</v>
@@ -4331,13 +4328,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="4" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D175" s="6">
         <v>80000</v>
@@ -4345,13 +4342,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="4" t="s">
-        <v>176</v>
+        <v>237</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D176" s="6">
         <v>60000</v>
@@ -4359,13 +4356,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="4" t="s">
-        <v>177</v>
+        <v>238</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D177" s="6">
         <v>60000</v>
@@ -4373,13 +4370,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="4" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D178" s="6">
         <v>60000</v>
@@ -4387,13 +4384,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="4" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D179" s="6">
         <v>100000</v>
@@ -4401,13 +4398,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="4" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D180" s="6">
         <v>95000</v>
@@ -4415,13 +4412,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="4" t="s">
-        <v>178</v>
+        <v>239</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D181" s="6">
         <v>85000</v>
@@ -4429,13 +4426,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="4" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="B182" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D182" s="6">
         <v>60000</v>
@@ -4443,13 +4440,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="4" t="s">
-        <v>179</v>
+        <v>240</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D183" s="6">
         <v>120000</v>
@@ -4457,13 +4454,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="4" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D184" s="6">
         <v>65000</v>
@@ -4471,13 +4468,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="4" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D185" s="6">
         <v>70000</v>
@@ -4485,13 +4482,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="4" t="s">
-        <v>181</v>
+        <v>242</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D186" s="6">
         <v>80000</v>
@@ -4499,13 +4496,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="4" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D187" s="6">
         <v>125000</v>
@@ -4513,13 +4510,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="4" t="s">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D188" s="6">
         <v>80000</v>
@@ -4527,13 +4524,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="4" t="s">
-        <v>185</v>
+        <v>245</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D189" s="6">
         <v>65000</v>
@@ -4541,13 +4538,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="4" t="s">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D190" s="6">
         <v>70000</v>
@@ -4555,13 +4552,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="4" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D191" s="6">
         <v>130000</v>
@@ -4569,13 +4566,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="4" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>188</v>
+        <v>76</v>
       </c>
       <c r="D192" s="6">
         <v>100000</v>
@@ -4583,13 +4580,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="4" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="B193" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C193" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D193" s="6">
         <v>65000</v>
@@ -4597,13 +4594,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="4" t="s">
-        <v>187</v>
+        <v>247</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D194" s="6">
         <v>65000</v>
@@ -4611,13 +4608,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="4" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="B195" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C195" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C195" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="D195" s="6">
         <v>65000</v>
@@ -4625,13 +4622,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="4" t="s">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D196" s="6">
         <v>85000</v>
@@ -4639,13 +4636,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="4" t="s">
-        <v>189</v>
+        <v>248</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D197" s="6">
         <v>120000</v>
@@ -4653,13 +4650,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="4" t="s">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D198" s="6">
         <v>70000</v>
@@ -4667,13 +4664,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="4" t="s">
-        <v>192</v>
+        <v>251</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D199" s="6">
         <v>90000</v>
@@ -4681,13 +4678,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="4" t="s">
-        <v>193</v>
+        <v>252</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D200" s="6">
         <v>90000</v>
@@ -4695,13 +4692,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="4" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D201" s="6">
         <v>80000</v>
@@ -4709,13 +4706,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="4" t="s">
-        <v>194</v>
+        <v>253</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="D202" s="6">
         <v>100000</v>
@@ -4723,13 +4720,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="4" t="s">
-        <v>197</v>
+        <v>254</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D203" s="6">
         <v>95000</v>
@@ -4737,13 +4734,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="4" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D204" s="6">
         <v>75000</v>
@@ -4751,13 +4748,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="4" t="s">
-        <v>198</v>
+        <v>255</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D205" s="6">
         <v>100000</v>
@@ -4765,13 +4762,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="4" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D206" s="6">
         <v>75000</v>
@@ -4779,13 +4776,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="4" t="s">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D207" s="6">
         <v>85000</v>
@@ -4793,13 +4790,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="4" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D208" s="6">
         <v>75000</v>
@@ -4807,13 +4804,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="4" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D209" s="6">
         <v>90000</v>
@@ -4821,13 +4818,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="4" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D210" s="6">
         <v>85000</v>
@@ -4835,13 +4832,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="4" t="s">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>204</v>
+        <v>79</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="D211" s="6">
         <v>110000</v>
@@ -4849,13 +4846,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="4" t="s">
-        <v>206</v>
+        <v>261</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D212" s="6">
         <v>75000</v>
@@ -4863,13 +4860,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="4" t="s">
-        <v>207</v>
+        <v>262</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D213" s="6">
         <v>80000</v>
@@ -4877,13 +4874,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="4" t="s">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>209</v>
+        <v>81</v>
       </c>
       <c r="D214" s="6">
         <v>90000</v>
@@ -4891,13 +4888,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="4" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D215" s="6">
         <v>95000</v>
@@ -4905,13 +4902,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="4" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D216" s="6">
         <v>85000</v>
@@ -4919,13 +4916,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="4" t="s">
-        <v>210</v>
+        <v>264</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D217" s="6">
         <v>120000</v>
@@ -4933,13 +4930,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="4" t="s">
-        <v>212</v>
+        <v>265</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D218" s="6">
         <v>120000</v>
@@ -4947,13 +4944,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="4" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D219" s="6">
         <v>110000</v>
@@ -4961,13 +4958,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="4" t="s">
-        <v>213</v>
+        <v>266</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D220" s="6">
         <v>120000</v>
@@ -4975,13 +4972,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="4" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D221" s="6">
         <v>110000</v>
@@ -4989,13 +4986,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="4" t="s">
-        <v>214</v>
+        <v>267</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D222" s="6">
         <v>130000</v>
@@ -5003,13 +5000,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="4" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D223" s="6">
         <v>110000</v>
@@ -5017,13 +5014,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="4" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D224" s="6">
         <v>95000</v>
@@ -5031,13 +5028,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="4" t="s">
-        <v>215</v>
+        <v>268</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="D225" s="6">
         <v>150000</v>
@@ -5045,13 +5042,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="4" t="s">
-        <v>217</v>
+        <v>269</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D226" s="6">
         <v>120000</v>
@@ -5059,13 +5056,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="4" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>133</v>
+        <v>56</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D227" s="6">
         <v>120000</v>
@@ -5073,13 +5070,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="4" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D228" s="6">
         <v>130000</v>
@@ -5087,13 +5084,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="4" t="s">
-        <v>218</v>
+        <v>270</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D229" s="6">
         <v>150000</v>
@@ -5101,13 +5098,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="4" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D230" s="6">
         <v>150000</v>
@@ -5115,13 +5112,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="4" t="s">
-        <v>220</v>
+        <v>272</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D231" s="6">
         <v>200000</v>
@@ -5129,13 +5126,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="4" t="s">
-        <v>221</v>
+        <v>273</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D232" s="6">
         <v>200000</v>
@@ -5143,10 +5140,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="4" t="s">
-        <v>222</v>
+        <v>274</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="6">
@@ -5155,13 +5152,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="4" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="D234" s="6">
         <v>110000</v>
@@ -5169,13 +5166,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="4" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>224</v>
+        <v>84</v>
       </c>
       <c r="D235" s="6">
         <v>110000</v>
@@ -5183,13 +5180,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="4" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>227</v>
+        <v>85</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="D236" s="6">
         <v>65000</v>
@@ -5197,13 +5194,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="4" t="s">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D237" s="6">
         <v>70000</v>
@@ -5211,13 +5208,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="4" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="D238" s="6">
         <v>65000</v>
@@ -5225,13 +5222,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="4" t="s">
-        <v>230</v>
+        <v>279</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D239" s="6">
         <v>60000</v>
@@ -5239,13 +5236,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="4" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D240" s="6">
         <v>65000</v>
@@ -5253,13 +5250,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="4" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D241" s="6">
         <v>125000</v>
@@ -5267,13 +5264,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="4" t="s">
-        <v>232</v>
+        <v>280</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D242" s="6">
         <v>110000</v>
@@ -5281,13 +5278,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="4" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D243" s="6">
         <v>70000</v>
@@ -5295,13 +5292,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="4" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D244" s="6">
         <v>110000</v>
@@ -5309,13 +5306,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="4" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D245" s="6">
         <v>105000</v>
@@ -5323,13 +5320,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="4" t="s">
-        <v>234</v>
+        <v>281</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D246" s="6">
         <v>125000</v>
@@ -5337,13 +5334,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="4" t="s">
-        <v>235</v>
+        <v>282</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D247" s="6">
         <v>70000</v>
@@ -5351,13 +5348,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="4" t="s">
-        <v>236</v>
+        <v>283</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="D248" s="6">
         <v>65000</v>
@@ -5365,13 +5362,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="4" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D249" s="6">
         <v>65000</v>
@@ -5379,13 +5376,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="4" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D250" s="6">
         <v>125000</v>
@@ -5393,13 +5390,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="4" t="s">
-        <v>238</v>
+        <v>284</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D251" s="6">
         <v>100000</v>
@@ -5407,13 +5404,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="4" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D252" s="6">
         <v>75000</v>
@@ -5421,13 +5418,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="4" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D253" s="6">
         <v>120000</v>
@@ -5435,13 +5432,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="4" t="s">
-        <v>239</v>
+        <v>285</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D254" s="6">
         <v>140000</v>
@@ -5449,13 +5446,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="4" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D255" s="6">
         <v>75000</v>
@@ -5463,13 +5460,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="4" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>241</v>
+        <v>90</v>
       </c>
       <c r="D256" s="6">
         <v>115000</v>
@@ -5477,13 +5474,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="4" t="s">
-        <v>240</v>
+        <v>286</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="D257" s="6">
         <v>135000</v>
@@ -5491,13 +5488,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="4" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D258" s="6">
         <v>80000</v>
@@ -5505,13 +5502,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="4" t="s">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D259" s="6">
         <v>90000</v>
@@ -5519,13 +5516,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="4" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D260" s="6">
         <v>135000</v>
@@ -5533,13 +5530,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="4" t="s">
-        <v>242</v>
+        <v>287</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D261" s="6">
         <v>120000</v>
@@ -5547,13 +5544,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="4" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D262" s="6">
         <v>85000</v>
@@ -5561,13 +5558,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="4" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D263" s="6">
         <v>95000</v>
@@ -5575,13 +5572,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="4" t="s">
-        <v>244</v>
+        <v>289</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>245</v>
+        <v>91</v>
       </c>
       <c r="D264" s="6">
         <v>150000</v>
@@ -5589,13 +5586,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="4" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>247</v>
+        <v>92</v>
       </c>
       <c r="D265" s="6">
         <v>110000</v>
@@ -5603,13 +5600,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="4" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>248</v>
+        <v>93</v>
       </c>
       <c r="D266" s="6">
         <v>120000</v>
@@ -5617,13 +5614,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="4" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D267" s="6">
         <v>110000</v>
@@ -5631,13 +5628,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="4" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D268" s="6">
         <v>130000</v>
@@ -5645,13 +5642,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="4" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D269" s="6">
         <v>70000</v>
@@ -5659,13 +5656,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="4" t="s">
-        <v>249</v>
+        <v>291</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D270" s="6">
         <v>110000</v>
@@ -5673,13 +5670,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="4" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D271" s="6">
         <v>80000</v>
@@ -5687,13 +5684,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="4" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D272" s="6">
         <v>125000</v>
@@ -5701,13 +5698,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="4" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>251</v>
+        <v>94</v>
       </c>
       <c r="D273" s="6">
         <v>145000</v>
@@ -5715,13 +5712,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="4" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D274" s="6">
         <v>130000</v>
@@ -5729,13 +5726,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="4" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D275" s="6">
         <v>80000</v>
@@ -5743,13 +5740,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="4" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>253</v>
+        <v>95</v>
       </c>
       <c r="D276" s="6">
         <v>150000</v>
@@ -5757,13 +5754,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="4" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>254</v>
+        <v>96</v>
       </c>
       <c r="D277" s="6">
         <v>140000</v>
@@ -5771,13 +5768,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D278" s="6">
         <v>95000</v>
@@ -5785,13 +5782,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D279" s="6">
         <v>85000</v>
@@ -5799,13 +5796,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>256</v>
+        <v>97</v>
       </c>
       <c r="D280" s="6">
         <v>145000</v>
@@ -5813,13 +5810,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="4" t="s">
-        <v>255</v>
+        <v>294</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D281" s="6">
         <v>130000</v>
@@ -5827,13 +5824,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="4" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D282" s="6">
         <v>85000</v>
@@ -5841,13 +5838,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="4" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>258</v>
+        <v>98</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D283" s="6">
         <v>95000</v>
@@ -5855,13 +5852,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="4" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="D284" s="6">
         <v>165000</v>
@@ -5869,13 +5866,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="4" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="D285" s="6">
         <v>125000</v>
@@ -5883,13 +5880,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="4" t="s">
-        <v>257</v>
+        <v>295</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="D286" s="6">
         <v>165000</v>
@@ -5897,13 +5894,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="4" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D287" s="6">
         <v>70000</v>
@@ -5911,13 +5908,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="4" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D288" s="6">
         <v>145000</v>
@@ -5925,13 +5922,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="4" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>263</v>
+        <v>101</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>264</v>
+        <v>102</v>
       </c>
       <c r="D289" s="6">
         <v>90000</v>
@@ -5939,13 +5936,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="4" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D290" s="6">
         <v>165000</v>
@@ -5953,13 +5950,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="4" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>245</v>
+        <v>91</v>
       </c>
       <c r="D291" s="6">
         <v>140000</v>
@@ -5967,13 +5964,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="4" t="s">
-        <v>265</v>
+        <v>298</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D292" s="6">
         <v>90000</v>
@@ -5981,13 +5978,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="4" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="D293" s="6">
         <v>100000</v>
@@ -5995,13 +5992,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="4" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D294" s="6">
         <v>90000</v>
@@ -6009,13 +6006,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="4" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="D295" s="6">
         <v>150000</v>
@@ -6023,13 +6020,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="4" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>269</v>
+        <v>105</v>
       </c>
       <c r="D296" s="6">
         <v>160000</v>
@@ -6037,13 +6034,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="4" t="s">
-        <v>266</v>
+        <v>299</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>270</v>
+        <v>106</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>271</v>
+        <v>107</v>
       </c>
       <c r="D297" s="6">
         <v>140000</v>
@@ -6051,13 +6048,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="4" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>267</v>
+        <v>103</v>
       </c>
       <c r="D298" s="6">
         <v>115000</v>
@@ -6065,10 +6062,10 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="4" t="s">
-        <v>272</v>
+        <v>300</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>258</v>
+        <v>98</v>
       </c>
       <c r="C299" s="1"/>
       <c r="D299" s="6">
@@ -6077,10 +6074,10 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="4" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="C300" s="1"/>
       <c r="D300" s="6">
@@ -6089,13 +6086,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="4" t="s">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D301" s="6">
         <v>120000</v>
@@ -6103,13 +6100,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="4" t="s">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D302" s="6">
         <v>130000</v>
@@ -6117,13 +6114,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" s="4" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D303" s="6">
         <v>145000</v>
@@ -6131,13 +6128,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="4" t="s">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="D304" s="6">
         <v>160000</v>
@@ -6145,13 +6142,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" s="4" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D305" s="6">
         <v>125000</v>
@@ -6159,13 +6156,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" s="4" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D306" s="6">
         <v>150000</v>
@@ -6173,13 +6170,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="4" t="s">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>268</v>
+        <v>104</v>
       </c>
       <c r="D307" s="6">
         <v>195000</v>
@@ -6187,13 +6184,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" s="4" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>279</v>
+        <v>109</v>
       </c>
       <c r="D308" s="6">
         <v>180000</v>
@@ -6201,13 +6198,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" s="4" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D309" s="6">
         <v>130000</v>
@@ -6215,13 +6212,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" s="4" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D310" s="6">
         <v>150000</v>
@@ -6229,13 +6226,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" s="4" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D311" s="6">
         <v>130000</v>
@@ -6243,13 +6240,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="4" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D312" s="6">
         <v>150000</v>
@@ -6257,13 +6254,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" s="4" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D313" s="6">
         <v>150000</v>
@@ -6271,13 +6268,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" s="4" t="s">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D314" s="6">
         <v>160000</v>
@@ -6285,13 +6282,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" s="4" t="s">
-        <v>285</v>
+        <v>310</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D315" s="6">
         <v>190000</v>
@@ -6299,13 +6296,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" s="4" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>153</v>
+        <v>67</v>
       </c>
       <c r="D316" s="6">
         <v>180000</v>
@@ -6313,13 +6310,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" s="4" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D317" s="6">
         <v>190000</v>
@@ -6327,13 +6324,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" s="4" t="s">
-        <v>288</v>
+        <v>313</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D318" s="6">
         <v>65000</v>
@@ -6341,13 +6338,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="4" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>231</v>
+        <v>87</v>
       </c>
       <c r="D319" s="6">
         <v>130000</v>
@@ -6355,13 +6352,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="4" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D320" s="6">
         <v>75000</v>
@@ -6369,13 +6366,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" s="4" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D321" s="6">
         <v>80000</v>
@@ -6383,13 +6380,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="4" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D322" s="6">
         <v>140000</v>
@@ -6397,13 +6394,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="4" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="D323" s="6">
         <v>140000</v>
@@ -6411,13 +6408,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="4" t="s">
-        <v>290</v>
+        <v>315</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="D324" s="6">
         <v>160000</v>
@@ -6425,13 +6422,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="4" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D325" s="6">
         <v>110000</v>
@@ -6439,13 +6436,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="4" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D326" s="6">
         <v>135000</v>
@@ -6453,13 +6450,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="4" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D327" s="6">
         <v>85000</v>
@@ -6467,13 +6464,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="4" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D328" s="6">
         <v>135000</v>
@@ -6481,13 +6478,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="4" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D329" s="6">
         <v>160000</v>
@@ -6495,13 +6492,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="4" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D330" s="6">
         <v>75000</v>
@@ -6509,13 +6506,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="4" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D331" s="6">
         <v>110000</v>
@@ -6523,13 +6520,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" s="4" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D332" s="6">
         <v>80000</v>
@@ -6537,13 +6534,13 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="4" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D333" s="6">
         <v>150000</v>
@@ -6551,13 +6548,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="4" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="D334" s="6">
         <v>135000</v>
@@ -6565,13 +6562,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="4" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D335" s="6">
         <v>115000</v>
@@ -6579,13 +6576,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="4" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>298</v>
+        <v>113</v>
       </c>
       <c r="D336" s="6">
         <v>180000</v>
@@ -6593,13 +6590,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" s="4" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D337" s="6">
         <v>140000</v>
@@ -6607,13 +6604,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" s="4" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>299</v>
+        <v>114</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c r="D338" s="6">
         <v>150000</v>
@@ -6621,13 +6618,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" s="4" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>302</v>
+        <v>116</v>
       </c>
       <c r="D339" s="6">
         <v>170000</v>
@@ -6635,13 +6632,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" s="4" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>303</v>
+        <v>117</v>
       </c>
       <c r="D340" s="6">
         <v>170000</v>
@@ -6649,13 +6646,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" s="4" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D341" s="6">
         <v>95000</v>
@@ -6663,13 +6660,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" s="4" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>304</v>
+        <v>118</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>305</v>
+        <v>119</v>
       </c>
       <c r="D342" s="6">
         <v>190000</v>
@@ -6677,13 +6674,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D343" s="6">
         <v>95000</v>
@@ -6691,13 +6688,13 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>259</v>
+        <v>99</v>
       </c>
       <c r="D344" s="6">
         <v>168000</v>
@@ -6705,13 +6702,13 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D345" s="6">
         <v>100000</v>
@@ -6719,13 +6716,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D346" s="6">
         <v>170000</v>
@@ -6733,13 +6730,13 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="D347" s="6">
         <v>135000</v>
@@ -6747,13 +6744,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D348" s="6">
         <v>80000</v>
@@ -6761,13 +6758,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D349" s="6">
         <v>85000</v>
@@ -6775,13 +6772,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="D350" s="6">
         <v>195000</v>
@@ -6789,13 +6786,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
       <c r="D351" s="6">
         <v>85000</v>
@@ -6803,13 +6800,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" s="4" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D352" s="6">
         <v>100000</v>
@@ -6817,13 +6814,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" s="4" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D353" s="6">
         <v>105000</v>
@@ -6831,13 +6828,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D354" s="6">
         <v>95000</v>
@@ -6845,13 +6842,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D355" s="6">
         <v>105000</v>
@@ -6859,13 +6856,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" s="4" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>302</v>
+        <v>116</v>
       </c>
       <c r="D356" s="6">
         <v>165000</v>
@@ -6873,13 +6870,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" s="4" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D357" s="6">
         <v>95000</v>
@@ -6887,13 +6884,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" s="4" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D358" s="6">
         <v>160000</v>
@@ -6901,13 +6898,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" s="4" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B359" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>315</v>
+        <v>121</v>
       </c>
       <c r="D359" s="6">
         <v>100000</v>
@@ -6915,13 +6912,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" s="4" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D360" s="6">
         <v>170000</v>
@@ -6929,13 +6926,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D361" s="6">
         <v>125000</v>
@@ -6943,13 +6940,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D362" s="6">
         <v>80000</v>
@@ -6957,13 +6954,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D363" s="6">
         <v>180000</v>
@@ -6971,13 +6968,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D364" s="6">
         <v>178000</v>
@@ -6985,13 +6982,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>318</v>
+        <v>122</v>
       </c>
       <c r="D365" s="6">
         <v>85000</v>
@@ -6999,13 +6996,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D366" s="6">
         <v>130000</v>
@@ -7013,13 +7010,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D367" s="6">
         <v>165000</v>
@@ -7027,13 +7024,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D368" s="6">
         <v>110000</v>
@@ -7041,13 +7038,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" s="4" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D369" s="6">
         <v>140000</v>
@@ -7055,13 +7052,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D370" s="6">
         <v>100000</v>
@@ -7069,10 +7066,10 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" s="4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C371" s="1"/>
       <c r="D371" s="6">
@@ -7081,13 +7078,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D372" s="6">
         <v>110000</v>
@@ -7095,13 +7092,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D373" s="6">
         <v>130000</v>
@@ -7109,13 +7106,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>302</v>
+        <v>116</v>
       </c>
       <c r="D374" s="6">
         <v>170000</v>
@@ -7123,13 +7120,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" s="4" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D375" s="6">
         <v>100000</v>
@@ -7137,13 +7134,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D376" s="6">
         <v>130000</v>
@@ -7151,13 +7148,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="D377" s="6">
         <v>190000</v>
@@ -7165,13 +7162,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>274</v>
+        <v>108</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>327</v>
+        <v>123</v>
       </c>
       <c r="D378" s="6">
         <v>100000</v>
@@ -7179,13 +7176,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>328</v>
+        <v>124</v>
       </c>
       <c r="D379" s="6">
         <v>200000</v>
@@ -7193,13 +7190,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="D380" s="6">
         <v>100000</v>
@@ -7207,13 +7204,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D381" s="6">
         <v>130000</v>
@@ -7221,13 +7218,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" s="4" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D382" s="6">
         <v>110000</v>
@@ -7235,13 +7232,13 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D383" s="6">
         <v>100000</v>
@@ -7249,13 +7246,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>216</v>
+        <v>83</v>
       </c>
       <c r="D384" s="6">
         <v>190000</v>
@@ -7263,13 +7260,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D385" s="6">
         <v>145000</v>
@@ -7277,13 +7274,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" s="4" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>334</v>
+        <v>125</v>
       </c>
       <c r="D386" s="6">
         <v>160000</v>
@@ -7291,13 +7288,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D387" s="6">
         <v>140000</v>
@@ -7305,13 +7302,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D388" s="6">
         <v>150000</v>
@@ -7319,13 +7316,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" s="4" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>337</v>
+        <v>126</v>
       </c>
       <c r="D389" s="6">
         <v>350000</v>
@@ -7333,13 +7330,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D390" s="6">
         <v>150000</v>
@@ -7347,13 +7344,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D391" s="6">
         <v>170000</v>
@@ -7361,13 +7358,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" s="4" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D392" s="6">
         <v>130000</v>
@@ -7375,13 +7372,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" s="4" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D393" s="6">
         <v>105000</v>
@@ -7389,13 +7386,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D394" s="6">
         <v>90000</v>
@@ -7403,13 +7400,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>343</v>
+        <v>127</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D395" s="6">
         <v>120000</v>
@@ -7417,13 +7414,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>344</v>
+        <v>128</v>
       </c>
       <c r="D396" s="6">
         <v>200000</v>
@@ -7431,13 +7428,13 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" s="4" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D397" s="6">
         <v>100000</v>
@@ -7445,13 +7442,13 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>292</v>
+        <v>112</v>
       </c>
       <c r="D398" s="6">
         <v>190000</v>
@@ -7459,13 +7456,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D399" s="6">
         <v>130000</v>
@@ -7473,13 +7470,13 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" s="4" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D400" s="6">
         <v>90000</v>
@@ -7487,13 +7484,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" s="4" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D401" s="6">
         <v>95000</v>
@@ -7501,13 +7498,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D402" s="6">
         <v>105000</v>
@@ -7515,13 +7512,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" s="4" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D403" s="6">
         <v>125000</v>
@@ -7529,13 +7526,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D404" s="6">
         <v>150000</v>
@@ -7543,13 +7540,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" s="4" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D405" s="6">
         <v>115000</v>
@@ -7557,13 +7554,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>269</v>
+        <v>105</v>
       </c>
       <c r="D406" s="6">
         <v>180000</v>
@@ -7571,13 +7568,13 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" s="4" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D407" s="6">
         <v>100000</v>
@@ -7585,13 +7582,13 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" s="4" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D408" s="6">
         <v>130000</v>
@@ -7599,13 +7596,13 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>353</v>
+        <v>129</v>
       </c>
       <c r="D409" s="6">
         <v>180000</v>
@@ -7613,13 +7610,13 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D410" s="6">
         <v>95000</v>
@@ -7627,13 +7624,13 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D411" s="6">
         <v>120000</v>
@@ -7641,13 +7638,13 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" s="4" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D412" s="6">
         <v>95000</v>
@@ -7655,13 +7652,13 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" s="4" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D413" s="6">
         <v>120000</v>
@@ -7669,13 +7666,13 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" s="4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D414" s="6">
         <v>120000</v>
@@ -7683,13 +7680,13 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" s="4" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D415" s="6">
         <v>140000</v>
@@ -7697,13 +7694,13 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" s="4" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D416" s="6">
         <v>110000</v>
@@ -7711,13 +7708,13 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D417" s="6">
         <v>150000</v>
@@ -7725,13 +7722,13 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" s="4" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="D418" s="6">
         <v>155000</v>
@@ -7739,13 +7736,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" s="4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D419" s="6">
         <v>110000</v>
@@ -7753,13 +7750,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" s="4" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D420" s="6">
         <v>165000</v>
@@ -7767,13 +7764,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="D421" s="6">
         <v>110000</v>
@@ -7781,13 +7778,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" s="4" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D422" s="6">
         <v>140000</v>
@@ -7795,13 +7792,13 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" s="4" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D423" s="6">
         <v>95000</v>
@@ -7809,13 +7806,13 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" s="4" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D424" s="6">
         <v>90000</v>
@@ -7823,13 +7820,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D425" s="6">
         <v>120000</v>
@@ -7837,13 +7834,13 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" s="4" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>364</v>
+        <v>130</v>
       </c>
       <c r="D426" s="6">
         <v>195000</v>
@@ -7851,13 +7848,13 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" s="4" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>237</v>
+        <v>89</v>
       </c>
       <c r="D427" s="6">
         <v>90000</v>
@@ -7865,13 +7862,13 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="D428" s="6">
         <v>120000</v>
@@ -7879,13 +7876,13 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" s="4" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D429" s="6">
         <v>165000</v>
@@ -7893,13 +7890,13 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D430" s="6">
         <v>110000</v>
@@ -7907,13 +7904,13 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" s="4" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>368</v>
+        <v>131</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D431" s="6">
         <v>180000</v>
@@ -7921,13 +7918,13 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D432" s="6">
         <v>110000</v>
@@ -7935,13 +7932,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D433" s="6">
         <v>130000</v>
@@ -7949,13 +7946,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D434" s="6">
         <v>120000</v>
@@ -7963,13 +7960,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>364</v>
+        <v>130</v>
       </c>
       <c r="D435" s="6">
         <v>210000</v>
@@ -7977,13 +7974,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" s="4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D436" s="6">
         <v>120000</v>
@@ -7991,13 +7988,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D437" s="6">
         <v>110000</v>
@@ -8005,13 +8002,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D438" s="6">
         <v>140000</v>
@@ -8019,13 +8016,13 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D439" s="6">
         <v>120000</v>
@@ -8033,13 +8030,13 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" s="4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D440" s="6">
         <v>140000</v>
@@ -8047,13 +8044,13 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>334</v>
+        <v>125</v>
       </c>
       <c r="D441" s="6">
         <v>135000</v>
@@ -8061,13 +8058,13 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" s="4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>378</v>
+        <v>133</v>
       </c>
       <c r="D442" s="6">
         <v>150000</v>
@@ -8075,13 +8072,13 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D443" s="6">
         <v>120000</v>
@@ -8089,13 +8086,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D444" s="6">
         <v>125000</v>
@@ -8103,13 +8100,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
       <c r="D445" s="6">
         <v>150000</v>
@@ -8117,13 +8114,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>382</v>
+        <v>134</v>
       </c>
       <c r="D446" s="6">
         <v>125000</v>
@@ -8131,13 +8128,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D447" s="6">
         <v>140000</v>
@@ -8145,13 +8142,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D448" s="6">
         <v>125000</v>
@@ -8159,13 +8156,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D449" s="6">
         <v>130000</v>
@@ -8173,13 +8170,13 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>386</v>
+        <v>135</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="D450" s="6">
         <v>180000</v>
@@ -8190,10 +8187,10 @@
         <v>387</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D451" s="6">
         <v>140000</v>
@@ -8204,10 +8201,10 @@
         <v>388</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>389</v>
+        <v>136</v>
       </c>
       <c r="D452" s="6">
         <v>120000</v>
@@ -8218,10 +8215,10 @@
         <v>388</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>282</v>
+        <v>110</v>
       </c>
       <c r="D453" s="6">
         <v>135000</v>
@@ -8229,13 +8226,13 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D454" s="6">
         <v>140000</v>
@@ -8243,13 +8240,13 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="D455" s="6">
         <v>150000</v>
@@ -8257,13 +8254,13 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="C456" s="1" t="s">
-        <v>315</v>
+        <v>121</v>
       </c>
       <c r="D456" s="6">
         <v>120000</v>
@@ -8271,13 +8268,13 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D457" s="6">
         <v>165000</v>
@@ -8285,13 +8282,13 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D458" s="6">
         <v>190000</v>
@@ -8299,13 +8296,13 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D459" s="6">
         <v>145000</v>
@@ -8313,13 +8310,13 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D460" s="6">
         <v>160000</v>
@@ -8327,13 +8324,13 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D461" s="6">
         <v>150000</v>
@@ -8341,13 +8338,13 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D462" s="6">
         <v>180000</v>
@@ -8355,13 +8352,13 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>165</v>
+        <v>70</v>
       </c>
       <c r="D463" s="6">
         <v>145000</v>
@@ -8369,13 +8366,13 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D464" s="6">
         <v>110000</v>
@@ -8383,13 +8380,13 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>372</v>
+        <v>132</v>
       </c>
       <c r="D465" s="6">
         <v>130000</v>
@@ -8397,13 +8394,13 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="D466" s="6">
         <v>145000</v>
@@ -8411,13 +8408,13 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" s="11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B467" s="12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="D467" s="13">
         <v>200000</v>

--- a/Webprecios/files/LISTA DE PRECIOS WEB.xlsx
+++ b/Webprecios/files/LISTA DE PRECIOS WEB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastián\Desktop\SAMCOR\TodoEnUnoCompania\Webprecios\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF43AC1E-3BF0-4922-8DB6-97A83517C8A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1442FB-B40E-4FB6-9797-468A3FE38D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{86DE79B7-439B-BB49-B2A1-21F166C3998A}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>MODELO</t>
   </si>
   <si>
-    <t>PRECIO</t>
-  </si>
-  <si>
     <t>CHINO</t>
   </si>
   <si>
@@ -1245,6 +1242,9 @@
   </si>
   <si>
     <t>33/12.50R22</t>
+  </si>
+  <si>
+    <t>UNIDAD</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1570,7 @@
     <tableColumn id="1" xr3:uid="{02E9608F-421E-44C5-9404-C679BF44AEB1}" name="MEDIDA" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{B1F8A53A-B13B-4A51-9F79-8D8EF4956E9C}" name="MARCA" dataDxfId="2"/>
     <tableColumn id="3" xr3:uid="{55DFEDBF-D19F-48E9-9EF1-52AC0DF1A0E7}" name="MODELO" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{DB7A0A06-AF64-47E9-9A7F-045CA06D591C}" name="PRECIO" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{DB7A0A06-AF64-47E9-9A7F-045CA06D591C}" name="UNIDAD" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1911,15 +1911,15 @@
         <v>2</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>3</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="6">
@@ -1928,13 +1928,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D3" s="6">
         <v>45000</v>
@@ -1942,13 +1942,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="6">
         <v>35000</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="6">
         <v>35000</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="D6" s="6">
         <v>50000</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D7" s="6">
         <v>40000</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="6">
         <v>40000</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D9" s="6">
         <v>50000</v>
@@ -2026,13 +2026,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="D10" s="6">
         <v>50000</v>
@@ -2040,13 +2040,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6">
         <v>55000</v>
@@ -2054,13 +2054,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" s="6">
         <v>50000</v>
@@ -2068,13 +2068,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="D13" s="6">
         <v>60000</v>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="6">
         <v>40000</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D15" s="6">
         <v>50000</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="6">
         <v>35000</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D17" s="6">
         <v>55000</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="6">
         <v>40000</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="6">
         <v>40000</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="6">
         <v>40000</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D21" s="6">
         <v>45000</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="D22" s="6">
         <v>50000</v>
@@ -2208,13 +2208,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D23" s="6">
         <v>70000</v>
@@ -2222,13 +2222,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="6">
         <v>55000</v>
@@ -2236,13 +2236,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="6">
         <v>40000</v>
@@ -2250,13 +2250,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D26" s="6">
         <v>60000</v>
@@ -2264,13 +2264,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D27" s="6">
         <v>65000</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="6">
         <v>45000</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D29" s="6">
         <v>55000</v>
@@ -2306,10 +2306,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="6">
@@ -2318,13 +2318,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="6">
         <v>45000</v>
@@ -2332,13 +2332,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="6">
         <v>40000</v>
@@ -2346,13 +2346,13 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D33" s="6">
         <v>45000</v>
@@ -2360,13 +2360,13 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D34" s="6">
         <v>40000</v>
@@ -2374,13 +2374,13 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D35" s="6">
         <v>55000</v>
@@ -2388,13 +2388,13 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D36" s="6">
         <v>60000</v>
@@ -2402,13 +2402,13 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" s="6">
         <v>70000</v>
@@ -2416,13 +2416,13 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D38" s="6">
         <v>45000</v>
@@ -2430,13 +2430,13 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D39" s="6">
         <v>75000</v>
@@ -2444,13 +2444,13 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D40" s="6">
         <v>60000</v>
@@ -2458,13 +2458,13 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D41" s="6">
         <v>45000</v>
@@ -2472,13 +2472,13 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D42" s="6">
         <v>60000</v>
@@ -2486,13 +2486,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D43" s="6">
         <v>55000</v>
@@ -2500,10 +2500,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="6">
@@ -2512,13 +2512,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D45" s="6">
         <v>45000</v>
@@ -2526,13 +2526,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46" s="6">
         <v>55000</v>
@@ -2540,13 +2540,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D47" s="6">
         <v>45000</v>
@@ -2554,13 +2554,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" s="6">
         <v>70000</v>
@@ -2568,13 +2568,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D49" s="6">
         <v>55000</v>
@@ -2582,13 +2582,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D50" s="6">
         <v>45000</v>
@@ -2596,13 +2596,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D51" s="6">
         <v>60000</v>
@@ -2610,13 +2610,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B52" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D52" s="6">
         <v>55000</v>
@@ -2624,13 +2624,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53" s="6">
         <v>77000</v>
@@ -2638,13 +2638,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D54" s="6">
         <v>65000</v>
@@ -2652,13 +2652,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D55" s="6">
         <v>50000</v>
@@ -2666,13 +2666,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D56" s="6">
         <v>50000</v>
@@ -2680,13 +2680,13 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D57" s="6">
         <v>80000</v>
@@ -2694,13 +2694,13 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D58" s="6">
         <v>55000</v>
@@ -2708,13 +2708,13 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D59" s="6">
         <v>45000</v>
@@ -2722,13 +2722,13 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" s="6">
         <v>75000</v>
@@ -2736,13 +2736,13 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D61" s="6">
         <v>60000</v>
@@ -2750,13 +2750,13 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D62" s="6">
         <v>45000</v>
@@ -2764,13 +2764,13 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D63" s="6">
         <v>50000</v>
@@ -2778,13 +2778,13 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D64" s="6">
         <v>70000</v>
@@ -2792,13 +2792,13 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D65" s="6">
         <v>65000</v>
@@ -2806,13 +2806,13 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D66" s="6">
         <v>75000</v>
@@ -2820,13 +2820,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D67" s="6">
         <v>80000</v>
@@ -2834,13 +2834,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D68" s="6">
         <v>50000</v>
@@ -2848,13 +2848,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D69" s="6">
         <v>50000</v>
@@ -2862,13 +2862,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D70" s="6">
         <v>63000</v>
@@ -2876,13 +2876,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D71" s="6">
         <v>75000</v>
@@ -2890,13 +2890,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B72" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C72" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D72" s="6">
         <v>80000</v>
@@ -2904,13 +2904,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C73" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D73" s="6">
         <v>60000</v>
@@ -2918,13 +2918,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D74" s="6">
         <v>75000</v>
@@ -2932,13 +2932,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D75" s="6">
         <v>65000</v>
@@ -2946,13 +2946,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D76" s="6">
         <v>75000</v>
@@ -2960,13 +2960,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D77" s="6">
         <v>80000</v>
@@ -2974,13 +2974,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B78" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D78" s="6">
         <v>90000</v>
@@ -2988,13 +2988,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D79" s="6">
         <v>50000</v>
@@ -3002,13 +3002,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D80" s="6">
         <v>55000</v>
@@ -3016,13 +3016,13 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D81" s="6">
         <v>50000</v>
@@ -3030,13 +3030,13 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D82" s="6">
         <v>50000</v>
@@ -3044,10 +3044,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="6">
@@ -3056,13 +3056,13 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D84" s="6">
         <v>75000</v>
@@ -3070,13 +3070,13 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D85" s="6">
         <v>50000</v>
@@ -3084,13 +3084,13 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D86" s="6">
         <v>85000</v>
@@ -3098,13 +3098,13 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D87" s="6">
         <v>85000</v>
@@ -3112,13 +3112,13 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D88" s="6">
         <v>70000</v>
@@ -3126,13 +3126,13 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D89" s="6">
         <v>75000</v>
@@ -3140,13 +3140,13 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D90" s="6">
         <v>50000</v>
@@ -3154,13 +3154,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D91" s="6">
         <v>50000</v>
@@ -3168,13 +3168,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D92" s="6">
         <v>85000</v>
@@ -3182,13 +3182,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D93" s="6">
         <v>80000</v>
@@ -3196,13 +3196,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D94" s="6">
         <v>70000</v>
@@ -3210,13 +3210,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D95" s="7">
         <v>50000</v>
@@ -3224,13 +3224,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D96" s="7">
         <v>80000</v>
@@ -3238,13 +3238,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D97" s="7">
         <v>50000</v>
@@ -3252,13 +3252,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D98" s="6">
         <v>95000</v>
@@ -3266,13 +3266,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D99" s="6">
         <v>70000</v>
@@ -3280,13 +3280,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D100" s="6">
         <v>75000</v>
@@ -3294,13 +3294,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D101" s="6">
         <v>55000</v>
@@ -3308,13 +3308,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D102" s="6">
         <v>50000</v>
@@ -3322,13 +3322,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103" s="6">
         <v>100000</v>
@@ -3336,13 +3336,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D104" s="6">
         <v>75000</v>
@@ -3350,13 +3350,13 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B105" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D105" s="6">
         <v>53000</v>
@@ -3364,13 +3364,13 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D106" s="6">
         <v>53000</v>
@@ -3378,13 +3378,13 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D107" s="6">
         <v>75000</v>
@@ -3392,13 +3392,13 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D108" s="6">
         <v>70000</v>
@@ -3406,13 +3406,13 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D109" s="6">
         <v>50000</v>
@@ -3420,13 +3420,13 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D110" s="6">
         <v>50000</v>
@@ -3434,13 +3434,13 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D111" s="6">
         <v>75000</v>
@@ -3448,13 +3448,13 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D112" s="6">
         <v>85000</v>
@@ -3462,13 +3462,13 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D113" s="6">
         <v>55000</v>
@@ -3476,13 +3476,13 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D114" s="6">
         <v>75000</v>
@@ -3490,13 +3490,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D115" s="6">
         <v>75000</v>
@@ -3504,13 +3504,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D116" s="6">
         <v>85000</v>
@@ -3518,13 +3518,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D117" s="6">
         <v>90000</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D118" s="6">
         <v>55000</v>
@@ -3546,13 +3546,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D119" s="6">
         <v>105000</v>
@@ -3560,13 +3560,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D120" s="6">
         <v>55000</v>
@@ -3574,13 +3574,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D121" s="6">
         <v>75000</v>
@@ -3588,13 +3588,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D122" s="6">
         <v>65000</v>
@@ -3602,13 +3602,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D123" s="6">
         <v>55000</v>
@@ -3616,13 +3616,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D124" s="6">
         <v>70000</v>
@@ -3630,13 +3630,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D125" s="6">
         <v>55000</v>
@@ -3644,13 +3644,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D126" s="6">
         <v>90000</v>
@@ -3658,13 +3658,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D127" s="6">
         <v>75000</v>
@@ -3672,13 +3672,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D128" s="6">
         <v>65000</v>
@@ -3686,13 +3686,13 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D129" s="6">
         <v>75000</v>
@@ -3700,13 +3700,13 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D130" s="6">
         <v>85000</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D131" s="6">
         <v>65000</v>
@@ -3728,13 +3728,13 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D132" s="6">
         <v>65000</v>
@@ -3742,13 +3742,13 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D133" s="6">
         <v>75000</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B134" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="D134" s="6">
         <v>80000</v>
@@ -3770,13 +3770,13 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D135" s="6">
         <v>70000</v>
@@ -3784,13 +3784,13 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D136" s="6">
         <v>100000</v>
@@ -3798,13 +3798,13 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D137" s="6">
         <v>85000</v>
@@ -3812,13 +3812,13 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B138" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C138" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C138" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D138" s="6">
         <v>90000</v>
@@ -3826,13 +3826,13 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D139" s="6">
         <v>70000</v>
@@ -3840,13 +3840,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D140" s="6">
         <v>95000</v>
@@ -3854,13 +3854,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D141" s="6">
         <v>110000</v>
@@ -3868,13 +3868,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D142" s="6">
         <v>80000</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D143" s="6">
         <v>110000</v>
@@ -3896,13 +3896,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D144" s="6">
         <v>160000</v>
@@ -3910,13 +3910,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D145" s="6">
         <v>110000</v>
@@ -3924,13 +3924,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D146" s="6">
         <v>95000</v>
@@ -3938,13 +3938,13 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D147" s="6">
         <v>170000</v>
@@ -3952,13 +3952,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D148" s="6">
         <v>190000</v>
@@ -3966,13 +3966,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D149" s="6">
         <v>120000</v>
@@ -3980,13 +3980,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D150" s="6">
         <v>120000</v>
@@ -3994,13 +3994,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D151" s="6">
         <v>110000</v>
@@ -4008,13 +4008,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D152" s="6">
         <v>150000</v>
@@ -4022,13 +4022,13 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D153" s="6">
         <v>165000</v>
@@ -4036,13 +4036,13 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D154" s="6">
         <v>175000</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="6">
@@ -4062,13 +4062,13 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D156" s="6">
         <v>60000</v>
@@ -4076,13 +4076,13 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D157" s="6">
         <v>90000</v>
@@ -4090,13 +4090,13 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D158" s="6">
         <v>60000</v>
@@ -4104,13 +4104,13 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D159" s="6">
         <v>95000</v>
@@ -4118,13 +4118,13 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D160" s="6">
         <v>95000</v>
@@ -4132,13 +4132,13 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D161" s="6">
         <v>60000</v>
@@ -4146,13 +4146,13 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D162" s="6">
         <v>80000</v>
@@ -4160,13 +4160,13 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D163" s="6">
         <v>60000</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D164" s="6">
         <v>60000</v>
@@ -4188,13 +4188,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D165" s="6">
         <v>100000</v>
@@ -4202,13 +4202,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D166" s="6">
         <v>85000</v>
@@ -4216,13 +4216,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D167" s="6">
         <v>60000</v>
@@ -4230,13 +4230,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="D168" s="6">
         <v>100000</v>
@@ -4244,13 +4244,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D169" s="6">
         <v>90000</v>
@@ -4258,13 +4258,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D170" s="6">
         <v>110000</v>
@@ -4272,13 +4272,13 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D171" s="6">
         <v>75000</v>
@@ -4286,13 +4286,13 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D172" s="6">
         <v>75000</v>
@@ -4300,13 +4300,13 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D173" s="6">
         <v>60000</v>
@@ -4314,13 +4314,13 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D174" s="6">
         <v>75000</v>
@@ -4328,13 +4328,13 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D175" s="6">
         <v>80000</v>
@@ -4342,13 +4342,13 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D176" s="6">
         <v>60000</v>
@@ -4356,13 +4356,13 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D177" s="6">
         <v>60000</v>
@@ -4370,13 +4370,13 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D178" s="6">
         <v>60000</v>
@@ -4384,13 +4384,13 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D179" s="6">
         <v>100000</v>
@@ -4398,13 +4398,13 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D180" s="6">
         <v>95000</v>
@@ -4412,13 +4412,13 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D181" s="6">
         <v>85000</v>
@@ -4426,13 +4426,13 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D182" s="6">
         <v>60000</v>
@@ -4440,13 +4440,13 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D183" s="6">
         <v>120000</v>
@@ -4454,13 +4454,13 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D184" s="6">
         <v>65000</v>
@@ -4468,13 +4468,13 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D185" s="6">
         <v>70000</v>
@@ -4482,13 +4482,13 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D186" s="6">
         <v>80000</v>
@@ -4496,13 +4496,13 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D187" s="6">
         <v>125000</v>
@@ -4510,13 +4510,13 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D188" s="6">
         <v>80000</v>
@@ -4524,13 +4524,13 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D189" s="6">
         <v>65000</v>
@@ -4538,13 +4538,13 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D190" s="6">
         <v>70000</v>
@@ -4552,13 +4552,13 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191" s="6">
         <v>130000</v>
@@ -4566,13 +4566,13 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D192" s="6">
         <v>100000</v>
@@ -4580,13 +4580,13 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D193" s="6">
         <v>65000</v>
@@ -4594,13 +4594,13 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D194" s="6">
         <v>65000</v>
@@ -4608,13 +4608,13 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D195" s="6">
         <v>65000</v>
@@ -4622,13 +4622,13 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D196" s="6">
         <v>85000</v>
@@ -4636,13 +4636,13 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D197" s="6">
         <v>120000</v>
@@ -4650,13 +4650,13 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D198" s="6">
         <v>70000</v>
@@ -4664,13 +4664,13 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D199" s="6">
         <v>90000</v>
@@ -4678,13 +4678,13 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D200" s="6">
         <v>90000</v>
@@ -4692,13 +4692,13 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D201" s="6">
         <v>80000</v>
@@ -4706,13 +4706,13 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D202" s="6">
         <v>100000</v>
@@ -4720,13 +4720,13 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D203" s="6">
         <v>95000</v>
@@ -4734,13 +4734,13 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D204" s="6">
         <v>75000</v>
@@ -4748,13 +4748,13 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D205" s="6">
         <v>100000</v>
@@ -4762,13 +4762,13 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D206" s="6">
         <v>75000</v>
@@ -4776,13 +4776,13 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D207" s="6">
         <v>85000</v>
@@ -4790,13 +4790,13 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D208" s="6">
         <v>75000</v>
@@ -4804,13 +4804,13 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D209" s="6">
         <v>90000</v>
@@ -4818,13 +4818,13 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D210" s="6">
         <v>85000</v>
@@ -4832,13 +4832,13 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B211" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C211" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="C211" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="D211" s="6">
         <v>110000</v>
@@ -4846,13 +4846,13 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D212" s="6">
         <v>75000</v>
@@ -4860,13 +4860,13 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D213" s="6">
         <v>80000</v>
@@ -4874,13 +4874,13 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D214" s="6">
         <v>90000</v>
@@ -4888,13 +4888,13 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D215" s="6">
         <v>95000</v>
@@ -4902,13 +4902,13 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D216" s="6">
         <v>85000</v>
@@ -4916,13 +4916,13 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D217" s="6">
         <v>120000</v>
@@ -4930,13 +4930,13 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D218" s="6">
         <v>120000</v>
@@ -4944,13 +4944,13 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B219" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C219" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D219" s="6">
         <v>110000</v>
@@ -4958,13 +4958,13 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D220" s="6">
         <v>120000</v>
@@ -4972,13 +4972,13 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B221" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C221" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="C221" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="D221" s="6">
         <v>110000</v>
@@ -4986,13 +4986,13 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D222" s="6">
         <v>130000</v>
@@ -5000,13 +5000,13 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D223" s="6">
         <v>110000</v>
@@ -5014,13 +5014,13 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D224" s="6">
         <v>95000</v>
@@ -5028,13 +5028,13 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D225" s="6">
         <v>150000</v>
@@ -5042,13 +5042,13 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D226" s="6">
         <v>120000</v>
@@ -5056,13 +5056,13 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D227" s="6">
         <v>120000</v>
@@ -5070,13 +5070,13 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D228" s="6">
         <v>130000</v>
@@ -5084,13 +5084,13 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D229" s="6">
         <v>150000</v>
@@ -5098,13 +5098,13 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D230" s="6">
         <v>150000</v>
@@ -5112,13 +5112,13 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D231" s="6">
         <v>200000</v>
@@ -5126,13 +5126,13 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D232" s="6">
         <v>200000</v>
@@ -5140,10 +5140,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C233" s="1"/>
       <c r="D233" s="6">
@@ -5152,13 +5152,13 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D234" s="6">
         <v>110000</v>
@@ -5166,13 +5166,13 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D235" s="6">
         <v>110000</v>
@@ -5180,13 +5180,13 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B236" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C236" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="D236" s="6">
         <v>65000</v>
@@ -5194,13 +5194,13 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D237" s="6">
         <v>70000</v>
@@ -5208,13 +5208,13 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D238" s="6">
         <v>65000</v>
@@ -5222,13 +5222,13 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D239" s="6">
         <v>60000</v>
@@ -5236,13 +5236,13 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D240" s="6">
         <v>65000</v>
@@ -5250,13 +5250,13 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D241" s="6">
         <v>125000</v>
@@ -5264,13 +5264,13 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D242" s="6">
         <v>110000</v>
@@ -5278,13 +5278,13 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D243" s="6">
         <v>70000</v>
@@ -5292,13 +5292,13 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D244" s="6">
         <v>110000</v>
@@ -5306,13 +5306,13 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D245" s="6">
         <v>105000</v>
@@ -5320,13 +5320,13 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D246" s="6">
         <v>125000</v>
@@ -5334,13 +5334,13 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D247" s="6">
         <v>70000</v>
@@ -5348,13 +5348,13 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D248" s="6">
         <v>65000</v>
@@ -5362,13 +5362,13 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D249" s="6">
         <v>65000</v>
@@ -5376,13 +5376,13 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D250" s="6">
         <v>125000</v>
@@ -5390,13 +5390,13 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C251" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D251" s="6">
         <v>100000</v>
@@ -5404,13 +5404,13 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D252" s="6">
         <v>75000</v>
@@ -5418,13 +5418,13 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D253" s="6">
         <v>120000</v>
@@ -5432,13 +5432,13 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D254" s="6">
         <v>140000</v>
@@ -5446,13 +5446,13 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D255" s="6">
         <v>75000</v>
@@ -5460,13 +5460,13 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D256" s="6">
         <v>115000</v>
@@ -5474,13 +5474,13 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D257" s="6">
         <v>135000</v>
@@ -5488,13 +5488,13 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D258" s="6">
         <v>80000</v>
@@ -5502,13 +5502,13 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D259" s="6">
         <v>90000</v>
@@ -5516,13 +5516,13 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D260" s="6">
         <v>135000</v>
@@ -5530,13 +5530,13 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D261" s="6">
         <v>120000</v>
@@ -5544,13 +5544,13 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D262" s="6">
         <v>85000</v>
@@ -5558,13 +5558,13 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D263" s="6">
         <v>95000</v>
@@ -5572,13 +5572,13 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D264" s="6">
         <v>150000</v>
@@ -5586,13 +5586,13 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D265" s="6">
         <v>110000</v>
@@ -5600,13 +5600,13 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D266" s="6">
         <v>120000</v>
@@ -5614,13 +5614,13 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D267" s="6">
         <v>110000</v>
@@ -5628,13 +5628,13 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D268" s="6">
         <v>130000</v>
@@ -5642,13 +5642,13 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D269" s="6">
         <v>70000</v>
@@ -5656,13 +5656,13 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D270" s="6">
         <v>110000</v>
@@ -5670,13 +5670,13 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D271" s="6">
         <v>80000</v>
@@ -5684,13 +5684,13 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D272" s="6">
         <v>125000</v>
@@ -5698,13 +5698,13 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D273" s="6">
         <v>145000</v>
@@ -5712,13 +5712,13 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D274" s="6">
         <v>130000</v>
@@ -5726,13 +5726,13 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D275" s="6">
         <v>80000</v>
@@ -5740,13 +5740,13 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D276" s="6">
         <v>150000</v>
@@ -5754,13 +5754,13 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D277" s="6">
         <v>140000</v>
@@ -5768,13 +5768,13 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D278" s="6">
         <v>95000</v>
@@ -5782,13 +5782,13 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D279" s="6">
         <v>85000</v>
@@ -5796,13 +5796,13 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D280" s="6">
         <v>145000</v>
@@ -5810,13 +5810,13 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D281" s="6">
         <v>130000</v>
@@ -5824,13 +5824,13 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D282" s="6">
         <v>85000</v>
@@ -5838,13 +5838,13 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D283" s="6">
         <v>95000</v>
@@ -5852,13 +5852,13 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D284" s="6">
         <v>165000</v>
@@ -5866,13 +5866,13 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D285" s="6">
         <v>125000</v>
@@ -5880,13 +5880,13 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D286" s="6">
         <v>165000</v>
@@ -5894,13 +5894,13 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D287" s="6">
         <v>70000</v>
@@ -5908,13 +5908,13 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D288" s="6">
         <v>145000</v>
@@ -5922,13 +5922,13 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B289" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C289" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="C289" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="D289" s="6">
         <v>90000</v>
@@ -5936,13 +5936,13 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D290" s="6">
         <v>165000</v>
@@ -5950,13 +5950,13 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D291" s="6">
         <v>140000</v>
@@ -5964,13 +5964,13 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D292" s="6">
         <v>90000</v>
@@ -5978,13 +5978,13 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D293" s="6">
         <v>100000</v>
@@ -5992,13 +5992,13 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D294" s="6">
         <v>90000</v>
@@ -6006,13 +6006,13 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D295" s="6">
         <v>150000</v>
@@ -6020,13 +6020,13 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D296" s="6">
         <v>160000</v>
@@ -6034,13 +6034,13 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B297" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C297" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="D297" s="6">
         <v>140000</v>
@@ -6048,13 +6048,13 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D298" s="6">
         <v>115000</v>
@@ -6062,10 +6062,10 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C299" s="1"/>
       <c r="D299" s="6">
@@ -6074,10 +6074,10 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C300" s="1"/>
       <c r="D300" s="6">
@@ -6086,13 +6086,13 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D301" s="6">
         <v>120000</v>
@@ -6100,13 +6100,13 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D302" s="6">
         <v>130000</v>
@@ -6114,13 +6114,13 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D303" s="6">
         <v>145000</v>
@@ -6128,13 +6128,13 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D304" s="6">
         <v>160000</v>
@@ -6142,13 +6142,13 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D305" s="6">
         <v>125000</v>
@@ -6156,13 +6156,13 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D306" s="6">
         <v>150000</v>
@@ -6170,13 +6170,13 @@
     </row>
     <row r="307" spans="1:4">
       <c r="A307" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D307" s="6">
         <v>195000</v>
@@ -6184,13 +6184,13 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D308" s="6">
         <v>180000</v>
@@ -6198,13 +6198,13 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D309" s="6">
         <v>130000</v>
@@ -6212,13 +6212,13 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D310" s="6">
         <v>150000</v>
@@ -6226,13 +6226,13 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D311" s="6">
         <v>130000</v>
@@ -6240,13 +6240,13 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D312" s="6">
         <v>150000</v>
@@ -6254,13 +6254,13 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D313" s="6">
         <v>150000</v>
@@ -6268,13 +6268,13 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D314" s="6">
         <v>160000</v>
@@ -6282,13 +6282,13 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D315" s="6">
         <v>190000</v>
@@ -6296,13 +6296,13 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D316" s="6">
         <v>180000</v>
@@ -6310,13 +6310,13 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D317" s="6">
         <v>190000</v>
@@ -6324,13 +6324,13 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D318" s="6">
         <v>65000</v>
@@ -6338,13 +6338,13 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D319" s="6">
         <v>130000</v>
@@ -6352,13 +6352,13 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D320" s="6">
         <v>75000</v>
@@ -6366,13 +6366,13 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D321" s="6">
         <v>80000</v>
@@ -6380,13 +6380,13 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D322" s="6">
         <v>140000</v>
@@ -6394,13 +6394,13 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D323" s="6">
         <v>140000</v>
@@ -6408,13 +6408,13 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D324" s="6">
         <v>160000</v>
@@ -6422,13 +6422,13 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D325" s="6">
         <v>110000</v>
@@ -6436,13 +6436,13 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D326" s="6">
         <v>135000</v>
@@ -6450,13 +6450,13 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D327" s="6">
         <v>85000</v>
@@ -6464,13 +6464,13 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D328" s="6">
         <v>135000</v>
@@ -6478,13 +6478,13 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D329" s="6">
         <v>160000</v>
@@ -6492,13 +6492,13 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D330" s="6">
         <v>75000</v>
@@ -6506,13 +6506,13 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D331" s="6">
         <v>110000</v>
@@ -6520,13 +6520,13 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D332" s="6">
         <v>80000</v>
@@ -6534,13 +6534,13 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D333" s="6">
         <v>150000</v>
@@ -6548,13 +6548,13 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D334" s="6">
         <v>135000</v>
@@ -6562,13 +6562,13 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D335" s="6">
         <v>115000</v>
@@ -6576,13 +6576,13 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D336" s="6">
         <v>180000</v>
@@ -6590,13 +6590,13 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D337" s="6">
         <v>140000</v>
@@ -6604,13 +6604,13 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B338" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C338" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="C338" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="D338" s="6">
         <v>150000</v>
@@ -6618,13 +6618,13 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D339" s="6">
         <v>170000</v>
@@ -6632,13 +6632,13 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D340" s="6">
         <v>170000</v>
@@ -6646,13 +6646,13 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D341" s="6">
         <v>95000</v>
@@ -6660,13 +6660,13 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B342" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C342" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="C342" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="D342" s="6">
         <v>190000</v>
@@ -6674,13 +6674,13 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D343" s="6">
         <v>95000</v>
@@ -6688,13 +6688,13 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D344" s="6">
         <v>168000</v>
@@ -6702,13 +6702,13 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D345" s="6">
         <v>100000</v>
@@ -6716,13 +6716,13 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D346" s="6">
         <v>170000</v>
@@ -6730,13 +6730,13 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D347" s="6">
         <v>135000</v>
@@ -6744,13 +6744,13 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D348" s="6">
         <v>80000</v>
@@ -6758,13 +6758,13 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D349" s="6">
         <v>85000</v>
@@ -6772,13 +6772,13 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D350" s="6">
         <v>195000</v>
@@ -6786,13 +6786,13 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B351" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C351" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C351" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D351" s="6">
         <v>85000</v>
@@ -6800,13 +6800,13 @@
     </row>
     <row r="352" spans="1:4">
       <c r="A352" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D352" s="6">
         <v>100000</v>
@@ -6814,13 +6814,13 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D353" s="6">
         <v>105000</v>
@@ -6828,13 +6828,13 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D354" s="6">
         <v>95000</v>
@@ -6842,13 +6842,13 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B355" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C355" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="D355" s="6">
         <v>105000</v>
@@ -6856,13 +6856,13 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D356" s="6">
         <v>165000</v>
@@ -6870,13 +6870,13 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D357" s="6">
         <v>95000</v>
@@ -6884,13 +6884,13 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D358" s="6">
         <v>160000</v>
@@ -6898,13 +6898,13 @@
     </row>
     <row r="359" spans="1:4">
       <c r="A359" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B359" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C359" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="D359" s="6">
         <v>100000</v>
@@ -6912,13 +6912,13 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B360" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D360" s="6">
         <v>170000</v>
@@ -6926,13 +6926,13 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B361" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D361" s="6">
         <v>125000</v>
@@ -6940,13 +6940,13 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D362" s="6">
         <v>80000</v>
@@ -6954,13 +6954,13 @@
     </row>
     <row r="363" spans="1:4">
       <c r="A363" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D363" s="6">
         <v>180000</v>
@@ -6968,13 +6968,13 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B364" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D364" s="6">
         <v>178000</v>
@@ -6982,13 +6982,13 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B365" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D365" s="6">
         <v>85000</v>
@@ -6996,13 +6996,13 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B366" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D366" s="6">
         <v>130000</v>
@@ -7010,13 +7010,13 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B367" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D367" s="6">
         <v>165000</v>
@@ -7024,13 +7024,13 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B368" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D368" s="6">
         <v>110000</v>
@@ -7038,13 +7038,13 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B369" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D369" s="6">
         <v>140000</v>
@@ -7052,13 +7052,13 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D370" s="6">
         <v>100000</v>
@@ -7066,10 +7066,10 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B371" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C371" s="1"/>
       <c r="D371" s="6">
@@ -7078,13 +7078,13 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D372" s="6">
         <v>110000</v>
@@ -7092,13 +7092,13 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D373" s="6">
         <v>130000</v>
@@ -7106,13 +7106,13 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B374" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D374" s="6">
         <v>170000</v>
@@ -7120,13 +7120,13 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B375" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D375" s="6">
         <v>100000</v>
@@ -7134,13 +7134,13 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B376" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D376" s="6">
         <v>130000</v>
@@ -7148,13 +7148,13 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B377" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D377" s="6">
         <v>190000</v>
@@ -7162,13 +7162,13 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B378" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D378" s="6">
         <v>100000</v>
@@ -7176,13 +7176,13 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D379" s="6">
         <v>200000</v>
@@ -7190,13 +7190,13 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D380" s="6">
         <v>100000</v>
@@ -7204,13 +7204,13 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B381" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D381" s="6">
         <v>130000</v>
@@ -7218,13 +7218,13 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B382" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D382" s="6">
         <v>110000</v>
@@ -7232,13 +7232,13 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B383" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D383" s="6">
         <v>100000</v>
@@ -7246,13 +7246,13 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B384" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D384" s="6">
         <v>190000</v>
@@ -7260,13 +7260,13 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D385" s="6">
         <v>145000</v>
@@ -7274,13 +7274,13 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D386" s="6">
         <v>160000</v>
@@ -7288,13 +7288,13 @@
     </row>
     <row r="387" spans="1:4">
       <c r="A387" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D387" s="6">
         <v>140000</v>
@@ -7302,13 +7302,13 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D388" s="6">
         <v>150000</v>
@@ -7316,13 +7316,13 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B389" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D389" s="6">
         <v>350000</v>
@@ -7330,13 +7330,13 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B390" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D390" s="6">
         <v>150000</v>
@@ -7344,13 +7344,13 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B391" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D391" s="6">
         <v>170000</v>
@@ -7358,13 +7358,13 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B392" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D392" s="6">
         <v>130000</v>
@@ -7372,13 +7372,13 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B393" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D393" s="6">
         <v>105000</v>
@@ -7386,13 +7386,13 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B394" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D394" s="6">
         <v>90000</v>
@@ -7400,13 +7400,13 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B395" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D395" s="6">
         <v>120000</v>
@@ -7414,13 +7414,13 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B396" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D396" s="6">
         <v>200000</v>
@@ -7428,13 +7428,13 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B397" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D397" s="6">
         <v>100000</v>
@@ -7442,13 +7442,13 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B398" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D398" s="6">
         <v>190000</v>
@@ -7456,13 +7456,13 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B399" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D399" s="6">
         <v>130000</v>
@@ -7470,13 +7470,13 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B400" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D400" s="6">
         <v>90000</v>
@@ -7484,13 +7484,13 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B401" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D401" s="6">
         <v>95000</v>
@@ -7498,13 +7498,13 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D402" s="6">
         <v>105000</v>
@@ -7512,13 +7512,13 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D403" s="6">
         <v>125000</v>
@@ -7526,13 +7526,13 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D404" s="6">
         <v>150000</v>
@@ -7540,13 +7540,13 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C405" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D405" s="6">
         <v>115000</v>
@@ -7554,13 +7554,13 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B406" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C406" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D406" s="6">
         <v>180000</v>
@@ -7568,13 +7568,13 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B407" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C407" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D407" s="6">
         <v>100000</v>
@@ -7582,13 +7582,13 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B408" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C408" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D408" s="6">
         <v>130000</v>
@@ -7596,13 +7596,13 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B409" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C409" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D409" s="6">
         <v>180000</v>
@@ -7610,13 +7610,13 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B410" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C410" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D410" s="6">
         <v>95000</v>
@@ -7624,13 +7624,13 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B411" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C411" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D411" s="6">
         <v>120000</v>
@@ -7638,13 +7638,13 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D412" s="6">
         <v>95000</v>
@@ -7652,13 +7652,13 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B413" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C413" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D413" s="6">
         <v>120000</v>
@@ -7666,13 +7666,13 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B414" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C414" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D414" s="6">
         <v>120000</v>
@@ -7680,13 +7680,13 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B415" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D415" s="6">
         <v>140000</v>
@@ -7694,13 +7694,13 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D416" s="6">
         <v>110000</v>
@@ -7708,13 +7708,13 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D417" s="6">
         <v>150000</v>
@@ -7722,13 +7722,13 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B418" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C418" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D418" s="6">
         <v>155000</v>
@@ -7736,13 +7736,13 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D419" s="6">
         <v>110000</v>
@@ -7750,13 +7750,13 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B420" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C420" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D420" s="6">
         <v>165000</v>
@@ -7764,13 +7764,13 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B421" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C421" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D421" s="6">
         <v>110000</v>
@@ -7778,13 +7778,13 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B422" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C422" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D422" s="6">
         <v>140000</v>
@@ -7792,13 +7792,13 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C423" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D423" s="6">
         <v>95000</v>
@@ -7806,13 +7806,13 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B424" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D424" s="6">
         <v>90000</v>
@@ -7820,13 +7820,13 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C425" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D425" s="6">
         <v>120000</v>
@@ -7834,13 +7834,13 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B426" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C426" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D426" s="6">
         <v>195000</v>
@@ -7848,13 +7848,13 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B427" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C427" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D427" s="6">
         <v>90000</v>
@@ -7862,13 +7862,13 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C428" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D428" s="6">
         <v>120000</v>
@@ -7876,13 +7876,13 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C429" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D429" s="6">
         <v>165000</v>
@@ -7890,13 +7890,13 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C430" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D430" s="6">
         <v>110000</v>
@@ -7904,13 +7904,13 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B431" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C431" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D431" s="6">
         <v>180000</v>
@@ -7918,13 +7918,13 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C432" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D432" s="6">
         <v>110000</v>
@@ -7932,13 +7932,13 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C433" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D433" s="6">
         <v>130000</v>
@@ -7946,13 +7946,13 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C434" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D434" s="6">
         <v>120000</v>
@@ -7960,13 +7960,13 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C435" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D435" s="6">
         <v>210000</v>
@@ -7974,13 +7974,13 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C436" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D436" s="6">
         <v>120000</v>
@@ -7988,13 +7988,13 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D437" s="6">
         <v>110000</v>
@@ -8002,13 +8002,13 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C438" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D438" s="6">
         <v>140000</v>
@@ -8016,13 +8016,13 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C439" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D439" s="6">
         <v>120000</v>
@@ -8030,13 +8030,13 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D440" s="6">
         <v>140000</v>
@@ -8044,13 +8044,13 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C441" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D441" s="6">
         <v>135000</v>
@@ -8058,13 +8058,13 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C442" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D442" s="6">
         <v>150000</v>
@@ -8072,13 +8072,13 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C443" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D443" s="6">
         <v>120000</v>
@@ -8086,13 +8086,13 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B444" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C444" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D444" s="6">
         <v>125000</v>
@@ -8100,13 +8100,13 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B445" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C445" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D445" s="6">
         <v>150000</v>
@@ -8114,13 +8114,13 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C446" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D446" s="6">
         <v>125000</v>
@@ -8128,13 +8128,13 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C447" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D447" s="6">
         <v>140000</v>
@@ -8142,13 +8142,13 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D448" s="6">
         <v>125000</v>
@@ -8156,13 +8156,13 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C449" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D449" s="6">
         <v>130000</v>
@@ -8170,13 +8170,13 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D450" s="6">
         <v>180000</v>
@@ -8184,13 +8184,13 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D451" s="6">
         <v>140000</v>
@@ -8198,13 +8198,13 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C452" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D452" s="6">
         <v>120000</v>
@@ -8212,13 +8212,13 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C453" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D453" s="6">
         <v>135000</v>
@@ -8226,13 +8226,13 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C454" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D454" s="6">
         <v>140000</v>
@@ -8240,13 +8240,13 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C455" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D455" s="6">
         <v>150000</v>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B456" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C456" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="D456" s="6">
         <v>120000</v>
@@ -8268,13 +8268,13 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C457" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D457" s="6">
         <v>165000</v>
@@ -8282,13 +8282,13 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C458" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D458" s="6">
         <v>190000</v>
@@ -8296,13 +8296,13 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B459" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C459" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D459" s="6">
         <v>145000</v>
@@ -8310,13 +8310,13 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C460" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D460" s="6">
         <v>160000</v>
@@ -8324,13 +8324,13 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D461" s="6">
         <v>150000</v>
@@ -8338,13 +8338,13 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C462" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D462" s="6">
         <v>180000</v>
@@ -8352,13 +8352,13 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D463" s="6">
         <v>145000</v>
@@ -8366,13 +8366,13 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C464" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D464" s="6">
         <v>110000</v>
@@ -8380,13 +8380,13 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C465" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D465" s="6">
         <v>130000</v>
@@ -8394,13 +8394,13 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C466" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D466" s="6">
         <v>145000</v>
@@ -8408,13 +8408,13 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467" s="11" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B467" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C467" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D467" s="13">
         <v>200000</v>
